--- a/Tabla_Morbilidad_TREE.xlsx
+++ b/Tabla_Morbilidad_TREE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Downloads\TABLERO_STREAMLIT_DASHBOARD\DASHBOARD_Morbilidad_DESPLIEGUE_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89EFBE3B-0C03-4004-B716-6C0A1FBE8278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{847F1715-D97D-4224-B190-01A192D02BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{944C2717-C2A7-4446-AED5-7F45A1436450}"/>
   </bookViews>
@@ -10471,7 +10471,7 @@
         <v>1506</v>
       </c>
       <c r="F2" s="8">
-        <v>930.5745000000004</v>
+        <v>930.57</v>
       </c>
       <c r="G2" s="8">
         <v>162</v>
@@ -10494,7 +10494,7 @@
         <v>1950</v>
       </c>
       <c r="F3" s="8">
-        <v>972.11400000000026</v>
+        <v>972.11</v>
       </c>
       <c r="G3" s="8">
         <v>200.99999999999997</v>
@@ -10517,7 +10517,7 @@
         <v>1302</v>
       </c>
       <c r="F4" s="8">
-        <v>724.87199999999996</v>
+        <v>724.87</v>
       </c>
       <c r="G4" s="8">
         <v>180</v>
@@ -10540,7 +10540,7 @@
         <v>1002</v>
       </c>
       <c r="F5" s="8">
-        <v>552.47539999999992</v>
+        <v>552.48</v>
       </c>
       <c r="G5" s="8">
         <v>181</v>
@@ -10563,7 +10563,7 @@
         <v>5754</v>
       </c>
       <c r="F6" s="8">
-        <v>3033.4683000000018</v>
+        <v>3033.47</v>
       </c>
       <c r="G6" s="8">
         <v>190</v>
@@ -10586,7 +10586,7 @@
         <v>420</v>
       </c>
       <c r="F7" s="8">
-        <v>209.82080000000008</v>
+        <v>209.82</v>
       </c>
       <c r="G7" s="8">
         <v>200</v>
@@ -10609,7 +10609,7 @@
         <v>4476</v>
       </c>
       <c r="F8" s="8">
-        <v>2226.4650000000001</v>
+        <v>2226.4699999999998</v>
       </c>
       <c r="G8" s="8">
         <v>200.99999999999997</v>
@@ -10632,7 +10632,7 @@
         <v>2742</v>
       </c>
       <c r="F9" s="8">
-        <v>1472.6306000000009</v>
+        <v>1472.63</v>
       </c>
       <c r="G9" s="8">
         <v>186</v>
@@ -10655,7 +10655,7 @@
         <v>1284</v>
       </c>
       <c r="F10" s="8">
-        <v>662.48180000000013</v>
+        <v>662.48</v>
       </c>
       <c r="G10" s="8">
         <v>194</v>
@@ -10678,7 +10678,7 @@
         <v>5010</v>
       </c>
       <c r="F11" s="8">
-        <v>2632.1193000000012</v>
+        <v>2632.12</v>
       </c>
       <c r="G11" s="8">
         <v>190</v>
@@ -10701,7 +10701,7 @@
         <v>1110</v>
       </c>
       <c r="F12" s="8">
-        <v>1084.257700000001</v>
+        <v>1084.26</v>
       </c>
       <c r="G12" s="8">
         <v>102</v>
@@ -10724,7 +10724,7 @@
         <v>3012</v>
       </c>
       <c r="F13" s="8">
-        <v>2823.6111000000001</v>
+        <v>2823.61</v>
       </c>
       <c r="G13" s="8">
         <v>107</v>
@@ -10747,7 +10747,7 @@
         <v>3174</v>
       </c>
       <c r="F14" s="8">
-        <v>2888.1951000000004</v>
+        <v>2888.2</v>
       </c>
       <c r="G14" s="8">
         <v>110.00000000000001</v>
@@ -10770,7 +10770,7 @@
         <v>1782</v>
       </c>
       <c r="F15" s="8">
-        <v>1469.9556000000007</v>
+        <v>1469.96</v>
       </c>
       <c r="G15" s="8">
         <v>121</v>
@@ -10793,7 +10793,7 @@
         <v>15714</v>
       </c>
       <c r="F16" s="8">
-        <v>16275.8773</v>
+        <v>16275.88</v>
       </c>
       <c r="G16" s="8">
         <v>97</v>
@@ -10816,7 +10816,7 @@
         <v>444</v>
       </c>
       <c r="F17" s="8">
-        <v>379.1601</v>
+        <v>379.16</v>
       </c>
       <c r="G17" s="8">
         <v>117</v>
@@ -10839,7 +10839,7 @@
         <v>8490</v>
       </c>
       <c r="F18" s="8">
-        <v>6894.7228999999988</v>
+        <v>6894.72</v>
       </c>
       <c r="G18" s="8">
         <v>123</v>
@@ -10862,7 +10862,7 @@
         <v>4890</v>
       </c>
       <c r="F19" s="8">
-        <v>4940.3441000000003</v>
+        <v>4940.34</v>
       </c>
       <c r="G19" s="8">
         <v>99</v>
@@ -10885,7 +10885,7 @@
         <v>2448</v>
       </c>
       <c r="F20" s="8">
-        <v>2180.5160000000005</v>
+        <v>2180.52</v>
       </c>
       <c r="G20" s="8">
         <v>112.00000000000001</v>
@@ -10908,7 +10908,7 @@
         <v>9756</v>
       </c>
       <c r="F21" s="8">
-        <v>9455.1167000000005</v>
+        <v>9455.1200000000008</v>
       </c>
       <c r="G21" s="8">
         <v>103</v>
@@ -10931,7 +10931,7 @@
         <v>2922</v>
       </c>
       <c r="F22" s="8">
-        <v>9592.9146999999975</v>
+        <v>9592.91</v>
       </c>
       <c r="G22" s="8">
         <v>30</v>
@@ -10954,7 +10954,7 @@
         <v>5790</v>
       </c>
       <c r="F23" s="8">
-        <v>19298.316999999988</v>
+        <v>19298.32</v>
       </c>
       <c r="G23" s="8">
         <v>30</v>
@@ -10977,7 +10977,7 @@
         <v>5214</v>
       </c>
       <c r="F24" s="8">
-        <v>17893.600099999985</v>
+        <v>17893.599999999999</v>
       </c>
       <c r="G24" s="8">
         <v>28.999999999999996</v>
@@ -11000,7 +11000,7 @@
         <v>3954</v>
       </c>
       <c r="F25" s="8">
-        <v>13421.439799999987</v>
+        <v>13421.44</v>
       </c>
       <c r="G25" s="8">
         <v>28.999999999999996</v>
@@ -11023,7 +11023,7 @@
         <v>19602</v>
       </c>
       <c r="F26" s="8">
-        <v>65780.099699999992</v>
+        <v>65780.100000000006</v>
       </c>
       <c r="G26" s="8">
         <v>30</v>
@@ -11046,7 +11046,7 @@
         <v>1122</v>
       </c>
       <c r="F27" s="8">
-        <v>3810.8624999999997</v>
+        <v>3810.86</v>
       </c>
       <c r="G27" s="8">
         <v>28.999999999999996</v>
@@ -11069,7 +11069,7 @@
         <v>13434</v>
       </c>
       <c r="F28" s="8">
-        <v>46340.948899999974</v>
+        <v>46340.95</v>
       </c>
       <c r="G28" s="8">
         <v>28.999999999999996</v>
@@ -11092,7 +11092,7 @@
         <v>7734</v>
       </c>
       <c r="F29" s="8">
-        <v>26695.925299999999</v>
+        <v>26695.93</v>
       </c>
       <c r="G29" s="8">
         <v>28.999999999999996</v>
@@ -11115,7 +11115,7 @@
         <v>7476</v>
       </c>
       <c r="F30" s="8">
-        <v>26593.646899999992</v>
+        <v>26593.65</v>
       </c>
       <c r="G30" s="8">
         <v>28.000000000000004</v>
@@ -11138,7 +11138,7 @@
         <v>24354</v>
       </c>
       <c r="F31" s="8">
-        <v>87011.332500000004</v>
+        <v>87011.33</v>
       </c>
       <c r="G31" s="8">
         <v>28.000000000000004</v>
@@ -11161,7 +11161,7 @@
         <v>90</v>
       </c>
       <c r="F32" s="8">
-        <v>21.826699999999995</v>
+        <v>21.83</v>
       </c>
       <c r="G32" s="8">
         <v>412</v>
@@ -11184,7 +11184,7 @@
         <v>144</v>
       </c>
       <c r="F33" s="8">
-        <v>32.016499999999994</v>
+        <v>32.020000000000003</v>
       </c>
       <c r="G33" s="8">
         <v>450</v>
@@ -11207,7 +11207,7 @@
         <v>96</v>
       </c>
       <c r="F34" s="8">
-        <v>38.278999999999996</v>
+        <v>38.28</v>
       </c>
       <c r="G34" s="8">
         <v>250.99999999999997</v>
@@ -11230,7 +11230,7 @@
         <v>96</v>
       </c>
       <c r="F35" s="8">
-        <v>22.146699999999996</v>
+        <v>22.15</v>
       </c>
       <c r="G35" s="8">
         <v>433</v>
@@ -11276,7 +11276,7 @@
         <v>78</v>
       </c>
       <c r="F37" s="8">
-        <v>28.985600000000002</v>
+        <v>28.99</v>
       </c>
       <c r="G37" s="8">
         <v>269</v>
@@ -11299,7 +11299,7 @@
         <v>180</v>
       </c>
       <c r="F38" s="8">
-        <v>79.391799999999989</v>
+        <v>79.39</v>
       </c>
       <c r="G38" s="8">
         <v>227</v>
@@ -11322,7 +11322,7 @@
         <v>366</v>
       </c>
       <c r="F39" s="8">
-        <v>113.34360000000002</v>
+        <v>113.34</v>
       </c>
       <c r="G39" s="8">
         <v>323</v>
@@ -11345,7 +11345,7 @@
         <v>66</v>
       </c>
       <c r="F40" s="8">
-        <v>24.008100000000002</v>
+        <v>24.01</v>
       </c>
       <c r="G40" s="8">
         <v>275</v>
@@ -11368,7 +11368,7 @@
         <v>594</v>
       </c>
       <c r="F41" s="8">
-        <v>235.06410000000005</v>
+        <v>235.06</v>
       </c>
       <c r="G41" s="8">
         <v>252.99999999999997</v>
@@ -11391,7 +11391,7 @@
         <v>2532</v>
       </c>
       <c r="F42" s="8">
-        <v>1708.1019000000024</v>
+        <v>1708.1</v>
       </c>
       <c r="G42" s="8">
         <v>148</v>
@@ -11414,7 +11414,7 @@
         <v>3402</v>
       </c>
       <c r="F43" s="8">
-        <v>1886.0000999999993</v>
+        <v>1886</v>
       </c>
       <c r="G43" s="8">
         <v>180</v>
@@ -11437,7 +11437,7 @@
         <v>1734</v>
       </c>
       <c r="F44" s="8">
-        <v>975.7246999999993</v>
+        <v>975.72</v>
       </c>
       <c r="G44" s="8">
         <v>178</v>
@@ -11460,7 +11460,7 @@
         <v>1620</v>
       </c>
       <c r="F45" s="8">
-        <v>886.63680000000011</v>
+        <v>886.64</v>
       </c>
       <c r="G45" s="8">
         <v>183</v>
@@ -11483,7 +11483,7 @@
         <v>8700</v>
       </c>
       <c r="F46" s="8">
-        <v>4936.2898999999961</v>
+        <v>4936.29</v>
       </c>
       <c r="G46" s="8">
         <v>176</v>
@@ -11506,7 +11506,7 @@
         <v>522</v>
       </c>
       <c r="F47" s="8">
-        <v>269.4668999999999</v>
+        <v>269.47000000000003</v>
       </c>
       <c r="G47" s="8">
         <v>194</v>
@@ -11529,7 +11529,7 @@
         <v>6654</v>
       </c>
       <c r="F48" s="8">
-        <v>3544.5157000000008</v>
+        <v>3544.52</v>
       </c>
       <c r="G48" s="8">
         <v>188</v>
@@ -11552,7 +11552,7 @@
         <v>4836</v>
       </c>
       <c r="F49" s="8">
-        <v>2860.8557000000001</v>
+        <v>2860.86</v>
       </c>
       <c r="G49" s="8">
         <v>169</v>
@@ -11598,7 +11598,7 @@
         <v>9108</v>
       </c>
       <c r="F51" s="8">
-        <v>5049.7563999999984</v>
+        <v>5049.76</v>
       </c>
       <c r="G51" s="8">
         <v>180</v>
@@ -11621,7 +11621,7 @@
         <v>1788</v>
       </c>
       <c r="F52" s="8">
-        <v>1776.4324000000008</v>
+        <v>1776.43</v>
       </c>
       <c r="G52" s="8">
         <v>101</v>
@@ -11644,7 +11644,7 @@
         <v>4470</v>
       </c>
       <c r="F53" s="8">
-        <v>4229.6719999999987</v>
+        <v>4229.67</v>
       </c>
       <c r="G53" s="8">
         <v>106</v>
@@ -11667,7 +11667,7 @@
         <v>4938</v>
       </c>
       <c r="F54" s="8">
-        <v>4614.0036000000018</v>
+        <v>4614</v>
       </c>
       <c r="G54" s="8">
         <v>107</v>
@@ -11690,7 +11690,7 @@
         <v>2244</v>
       </c>
       <c r="F55" s="8">
-        <v>1850.4481000000005</v>
+        <v>1850.45</v>
       </c>
       <c r="G55" s="8">
         <v>121</v>
@@ -11713,7 +11713,7 @@
         <v>21204</v>
       </c>
       <c r="F56" s="8">
-        <v>21656.285099999965</v>
+        <v>21656.29</v>
       </c>
       <c r="G56" s="8">
         <v>98</v>
@@ -11736,7 +11736,7 @@
         <v>876</v>
       </c>
       <c r="F57" s="8">
-        <v>850.60100000000034</v>
+        <v>850.6</v>
       </c>
       <c r="G57" s="8">
         <v>103</v>
@@ -11759,7 +11759,7 @@
         <v>13836</v>
       </c>
       <c r="F58" s="8">
-        <v>12442.914199999999</v>
+        <v>12442.91</v>
       </c>
       <c r="G58" s="8">
         <v>111.00000000000001</v>
@@ -11782,7 +11782,7 @@
         <v>11052</v>
       </c>
       <c r="F59" s="8">
-        <v>11579.318699999993</v>
+        <v>11579.32</v>
       </c>
       <c r="G59" s="8">
         <v>95</v>
@@ -11805,7 +11805,7 @@
         <v>4224</v>
       </c>
       <c r="F60" s="8">
-        <v>3877.6826000000028</v>
+        <v>3877.68</v>
       </c>
       <c r="G60" s="8">
         <v>109.00000000000001</v>
@@ -11828,7 +11828,7 @@
         <v>15486</v>
       </c>
       <c r="F61" s="8">
-        <v>15025.240399999991</v>
+        <v>15025.24</v>
       </c>
       <c r="G61" s="8">
         <v>103</v>
@@ -11851,7 +11851,7 @@
         <v>12414</v>
       </c>
       <c r="F62" s="8">
-        <v>42451.797099999923</v>
+        <v>42451.8</v>
       </c>
       <c r="G62" s="8">
         <v>28.999999999999996</v>
@@ -11874,7 +11874,7 @@
         <v>17148</v>
       </c>
       <c r="F63" s="8">
-        <v>53053.991799999989</v>
+        <v>53053.99</v>
       </c>
       <c r="G63" s="8">
         <v>32</v>
@@ -11897,7 +11897,7 @@
         <v>16986</v>
       </c>
       <c r="F64" s="8">
-        <v>55257.675800000005</v>
+        <v>55257.68</v>
       </c>
       <c r="G64" s="8">
         <v>31</v>
@@ -11920,7 +11920,7 @@
         <v>7536</v>
       </c>
       <c r="F65" s="8">
-        <v>24536.868400000028</v>
+        <v>24536.87</v>
       </c>
       <c r="G65" s="8">
         <v>31</v>
@@ -11943,7 +11943,7 @@
         <v>46062</v>
       </c>
       <c r="F66" s="8">
-        <v>151102.88229999994</v>
+        <v>151102.88</v>
       </c>
       <c r="G66" s="8">
         <v>30</v>
@@ -11966,7 +11966,7 @@
         <v>3144</v>
       </c>
       <c r="F67" s="8">
-        <v>9688.9731000000029</v>
+        <v>9688.9699999999993</v>
       </c>
       <c r="G67" s="8">
         <v>32</v>
@@ -11989,7 +11989,7 @@
         <v>35280</v>
       </c>
       <c r="F68" s="8">
-        <v>117411.58780000004</v>
+        <v>117411.59</v>
       </c>
       <c r="G68" s="8">
         <v>30</v>
@@ -12012,7 +12012,7 @@
         <v>21456</v>
       </c>
       <c r="F69" s="8">
-        <v>73807.524299999917</v>
+        <v>73807.520000000004</v>
       </c>
       <c r="G69" s="8">
         <v>28.999999999999996</v>
@@ -12035,7 +12035,7 @@
         <v>16650</v>
       </c>
       <c r="F70" s="8">
-        <v>54022.95259999999</v>
+        <v>54022.95</v>
       </c>
       <c r="G70" s="8">
         <v>31</v>
@@ -12058,7 +12058,7 @@
         <v>51288</v>
       </c>
       <c r="F71" s="8">
-        <v>175893.64479999989</v>
+        <v>175893.64</v>
       </c>
       <c r="G71" s="8">
         <v>28.999999999999996</v>
@@ -12081,7 +12081,7 @@
         <v>246</v>
       </c>
       <c r="F72" s="8">
-        <v>58.073300000000003</v>
+        <v>58.07</v>
       </c>
       <c r="G72" s="8">
         <v>424</v>
@@ -12104,7 +12104,7 @@
         <v>450</v>
       </c>
       <c r="F73" s="8">
-        <v>106.54520000000002</v>
+        <v>106.55</v>
       </c>
       <c r="G73" s="8">
         <v>422</v>
@@ -12127,7 +12127,7 @@
         <v>258</v>
       </c>
       <c r="F74" s="8">
-        <v>65.038099999999986</v>
+        <v>65.040000000000006</v>
       </c>
       <c r="G74" s="8">
         <v>397</v>
@@ -12150,7 +12150,7 @@
         <v>288</v>
       </c>
       <c r="F75" s="8">
-        <v>49.883099999999999</v>
+        <v>49.88</v>
       </c>
       <c r="G75" s="8">
         <v>577</v>
@@ -12173,7 +12173,7 @@
         <v>888</v>
       </c>
       <c r="F76" s="8">
-        <v>231.16060000000013</v>
+        <v>231.16</v>
       </c>
       <c r="G76" s="8">
         <v>384</v>
@@ -12196,7 +12196,7 @@
         <v>168</v>
       </c>
       <c r="F77" s="8">
-        <v>37.7485</v>
+        <v>37.75</v>
       </c>
       <c r="G77" s="8">
         <v>445</v>
@@ -12219,7 +12219,7 @@
         <v>504</v>
       </c>
       <c r="F78" s="8">
-        <v>169.23560000000001</v>
+        <v>169.24</v>
       </c>
       <c r="G78" s="8">
         <v>298</v>
@@ -12242,7 +12242,7 @@
         <v>936</v>
       </c>
       <c r="F79" s="8">
-        <v>220.23000000000013</v>
+        <v>220.23</v>
       </c>
       <c r="G79" s="8">
         <v>425</v>
@@ -12265,7 +12265,7 @@
         <v>180</v>
       </c>
       <c r="F80" s="8">
-        <v>51.150299999999994</v>
+        <v>51.15</v>
       </c>
       <c r="G80" s="8">
         <v>352</v>
@@ -12288,7 +12288,7 @@
         <v>1248</v>
       </c>
       <c r="F81" s="8">
-        <v>273.73680000000013</v>
+        <v>273.74</v>
       </c>
       <c r="G81" s="8">
         <v>455.99999999999994</v>
@@ -12311,7 +12311,7 @@
         <v>1824</v>
       </c>
       <c r="F82" s="8">
-        <v>1242.6680999999996</v>
+        <v>1242.67</v>
       </c>
       <c r="G82" s="8">
         <v>147</v>
@@ -12334,7 +12334,7 @@
         <v>2646</v>
       </c>
       <c r="F83" s="8">
-        <v>1431.1960000000001</v>
+        <v>1431.2</v>
       </c>
       <c r="G83" s="8">
         <v>185</v>
@@ -12357,7 +12357,7 @@
         <v>1296</v>
       </c>
       <c r="F84" s="8">
-        <v>721.75429999999994</v>
+        <v>721.75</v>
       </c>
       <c r="G84" s="8">
         <v>180</v>
@@ -12380,7 +12380,7 @@
         <v>1326</v>
       </c>
       <c r="F85" s="8">
-        <v>717.84869999999989</v>
+        <v>717.85</v>
       </c>
       <c r="G85" s="8">
         <v>185</v>
@@ -12403,7 +12403,7 @@
         <v>6246</v>
       </c>
       <c r="F86" s="8">
-        <v>3669.4824999999951</v>
+        <v>3669.48</v>
       </c>
       <c r="G86" s="8">
         <v>170</v>
@@ -12426,7 +12426,7 @@
         <v>498</v>
       </c>
       <c r="F87" s="8">
-        <v>261.37029999999999</v>
+        <v>261.37</v>
       </c>
       <c r="G87" s="8">
         <v>191</v>
@@ -12449,7 +12449,7 @@
         <v>4188</v>
       </c>
       <c r="F88" s="8">
-        <v>2260.2731999999992</v>
+        <v>2260.27</v>
       </c>
       <c r="G88" s="8">
         <v>185</v>
@@ -12472,7 +12472,7 @@
         <v>2916</v>
       </c>
       <c r="F89" s="8">
-        <v>1689.1880999999994</v>
+        <v>1689.19</v>
       </c>
       <c r="G89" s="8">
         <v>173</v>
@@ -12495,7 +12495,7 @@
         <v>2298</v>
       </c>
       <c r="F90" s="8">
-        <v>1298.9649999999997</v>
+        <v>1298.97</v>
       </c>
       <c r="G90" s="8">
         <v>177</v>
@@ -12518,7 +12518,7 @@
         <v>9948</v>
       </c>
       <c r="F91" s="8">
-        <v>5916.5149999999976</v>
+        <v>5916.52</v>
       </c>
       <c r="G91" s="8">
         <v>168</v>
@@ -12541,7 +12541,7 @@
         <v>1062</v>
       </c>
       <c r="F92" s="8">
-        <v>1150.2127999999987</v>
+        <v>1150.21</v>
       </c>
       <c r="G92" s="8">
         <v>92</v>
@@ -12564,7 +12564,7 @@
         <v>2172</v>
       </c>
       <c r="F93" s="8">
-        <v>2408.0915000000014</v>
+        <v>2408.09</v>
       </c>
       <c r="G93" s="8">
         <v>90</v>
@@ -12587,7 +12587,7 @@
         <v>1188</v>
       </c>
       <c r="F94" s="8">
-        <v>1198.8726999999994</v>
+        <v>1198.8699999999999</v>
       </c>
       <c r="G94" s="8">
         <v>99</v>
@@ -12610,7 +12610,7 @@
         <v>1182</v>
       </c>
       <c r="F95" s="8">
-        <v>1096.6052999999997</v>
+        <v>1096.6099999999999</v>
       </c>
       <c r="G95" s="8">
         <v>108</v>
@@ -12633,7 +12633,7 @@
         <v>10848</v>
       </c>
       <c r="F96" s="8">
-        <v>12697.307299999988</v>
+        <v>12697.31</v>
       </c>
       <c r="G96" s="8">
         <v>85</v>
@@ -12656,7 +12656,7 @@
         <v>402</v>
       </c>
       <c r="F97" s="8">
-        <v>425.45800000000003</v>
+        <v>425.46</v>
       </c>
       <c r="G97" s="8">
         <v>94</v>
@@ -12679,7 +12679,7 @@
         <v>4368</v>
       </c>
       <c r="F98" s="8">
-        <v>4153.9147999999986</v>
+        <v>4153.91</v>
       </c>
       <c r="G98" s="8">
         <v>105</v>
@@ -12702,7 +12702,7 @@
         <v>3174</v>
       </c>
       <c r="F99" s="8">
-        <v>3536.3525000000018</v>
+        <v>3536.35</v>
       </c>
       <c r="G99" s="8">
         <v>90</v>
@@ -12725,7 +12725,7 @@
         <v>2574</v>
       </c>
       <c r="F100" s="8">
-        <v>2777.7581</v>
+        <v>2777.76</v>
       </c>
       <c r="G100" s="8">
         <v>93</v>
@@ -12748,7 +12748,7 @@
         <v>10680</v>
       </c>
       <c r="F101" s="8">
-        <v>10960.373699999993</v>
+        <v>10960.37</v>
       </c>
       <c r="G101" s="8">
         <v>97</v>
@@ -12771,7 +12771,7 @@
         <v>11094</v>
       </c>
       <c r="F102" s="8">
-        <v>37240.8969</v>
+        <v>37240.9</v>
       </c>
       <c r="G102" s="8">
         <v>30</v>
@@ -12794,7 +12794,7 @@
         <v>17724</v>
       </c>
       <c r="F103" s="8">
-        <v>54420.704099999974</v>
+        <v>54420.7</v>
       </c>
       <c r="G103" s="8">
         <v>33</v>
@@ -12817,7 +12817,7 @@
         <v>11796</v>
       </c>
       <c r="F104" s="8">
-        <v>40090.667399999962</v>
+        <v>40090.67</v>
       </c>
       <c r="G104" s="8">
         <v>28.999999999999996</v>
@@ -12840,7 +12840,7 @@
         <v>5694</v>
       </c>
       <c r="F105" s="8">
-        <v>19037.611300000011</v>
+        <v>19037.61</v>
       </c>
       <c r="G105" s="8">
         <v>30</v>
@@ -12863,7 +12863,7 @@
         <v>40224</v>
       </c>
       <c r="F106" s="8">
-        <v>130734.97420000008</v>
+        <v>130734.97</v>
       </c>
       <c r="G106" s="8">
         <v>31</v>
@@ -12886,7 +12886,7 @@
         <v>2802</v>
       </c>
       <c r="F107" s="8">
-        <v>8951.7909999999993</v>
+        <v>8951.7900000000009</v>
       </c>
       <c r="G107" s="8">
         <v>31</v>
@@ -12909,7 +12909,7 @@
         <v>19326</v>
       </c>
       <c r="F108" s="8">
-        <v>65332.081799999985</v>
+        <v>65332.08</v>
       </c>
       <c r="G108" s="8">
         <v>30</v>
@@ -12932,7 +12932,7 @@
         <v>11856</v>
       </c>
       <c r="F109" s="8">
-        <v>40373.801599999984</v>
+        <v>40373.800000000003</v>
       </c>
       <c r="G109" s="8">
         <v>28.999999999999996</v>
@@ -12955,7 +12955,7 @@
         <v>15612</v>
       </c>
       <c r="F110" s="8">
-        <v>55649.521799999951</v>
+        <v>55649.52</v>
       </c>
       <c r="G110" s="8">
         <v>28.000000000000004</v>
@@ -12978,7 +12978,7 @@
         <v>50700</v>
       </c>
       <c r="F111" s="8">
-        <v>178024.39380000002</v>
+        <v>178024.39</v>
       </c>
       <c r="G111" s="8">
         <v>28.000000000000004</v>
@@ -13001,7 +13001,7 @@
         <v>132</v>
       </c>
       <c r="F112" s="8">
-        <v>30.852499999999999</v>
+        <v>30.85</v>
       </c>
       <c r="G112" s="8">
         <v>428</v>
@@ -13024,7 +13024,7 @@
         <v>408</v>
       </c>
       <c r="F113" s="8">
-        <v>88.472799999999992</v>
+        <v>88.47</v>
       </c>
       <c r="G113" s="8">
         <v>461.00000000000006</v>
@@ -13047,7 +13047,7 @@
         <v>216</v>
       </c>
       <c r="F114" s="8">
-        <v>51.3825</v>
+        <v>51.38</v>
       </c>
       <c r="G114" s="8">
         <v>420</v>
@@ -13070,7 +13070,7 @@
         <v>222</v>
       </c>
       <c r="F115" s="8">
-        <v>37.341499999999996</v>
+        <v>37.340000000000003</v>
       </c>
       <c r="G115" s="8">
         <v>595</v>
@@ -13093,7 +13093,7 @@
         <v>786</v>
       </c>
       <c r="F116" s="8">
-        <v>179.51519999999999</v>
+        <v>179.52</v>
       </c>
       <c r="G116" s="8">
         <v>438</v>
@@ -13116,7 +13116,7 @@
         <v>252</v>
       </c>
       <c r="F117" s="8">
-        <v>56.085599999999999</v>
+        <v>56.09</v>
       </c>
       <c r="G117" s="8">
         <v>449</v>
@@ -13139,7 +13139,7 @@
         <v>144</v>
       </c>
       <c r="F118" s="8">
-        <v>51.003500000000003</v>
+        <v>51</v>
       </c>
       <c r="G118" s="8">
         <v>282</v>
@@ -13162,7 +13162,7 @@
         <v>300</v>
       </c>
       <c r="F119" s="8">
-        <v>72.196099999999973</v>
+        <v>72.2</v>
       </c>
       <c r="G119" s="8">
         <v>416</v>
@@ -13185,7 +13185,7 @@
         <v>156</v>
       </c>
       <c r="F120" s="8">
-        <v>42.163299999999992</v>
+        <v>42.16</v>
       </c>
       <c r="G120" s="8">
         <v>370</v>
@@ -13208,7 +13208,7 @@
         <v>1752</v>
       </c>
       <c r="F121" s="8">
-        <v>331.61779999999993</v>
+        <v>331.62</v>
       </c>
       <c r="G121" s="8">
         <v>528</v>
@@ -13231,7 +13231,7 @@
         <v>2304</v>
       </c>
       <c r="F122" s="8">
-        <v>1613.7209999999991</v>
+        <v>1613.72</v>
       </c>
       <c r="G122" s="8">
         <v>143</v>
@@ -13254,7 +13254,7 @@
         <v>3588</v>
       </c>
       <c r="F123" s="8">
-        <v>2117.2655999999988</v>
+        <v>2117.27</v>
       </c>
       <c r="G123" s="8">
         <v>169</v>
@@ -13277,7 +13277,7 @@
         <v>2064</v>
       </c>
       <c r="F124" s="8">
-        <v>1150.0014999999999</v>
+        <v>1150</v>
       </c>
       <c r="G124" s="8">
         <v>179</v>
@@ -13300,7 +13300,7 @@
         <v>1866</v>
       </c>
       <c r="F125" s="8">
-        <v>1101.0567999999996</v>
+        <v>1101.06</v>
       </c>
       <c r="G125" s="8">
         <v>169</v>
@@ -13323,7 +13323,7 @@
         <v>10722</v>
       </c>
       <c r="F126" s="8">
-        <v>6258.0593999999983</v>
+        <v>6258.06</v>
       </c>
       <c r="G126" s="8">
         <v>171</v>
@@ -13346,7 +13346,7 @@
         <v>720</v>
       </c>
       <c r="F127" s="8">
-        <v>404.48889999999983</v>
+        <v>404.49</v>
       </c>
       <c r="G127" s="8">
         <v>178</v>
@@ -13369,7 +13369,7 @@
         <v>8010</v>
       </c>
       <c r="F128" s="8">
-        <v>4369.7731999999978</v>
+        <v>4369.7700000000004</v>
       </c>
       <c r="G128" s="8">
         <v>183</v>
@@ -13392,7 +13392,7 @@
         <v>4596</v>
       </c>
       <c r="F129" s="8">
-        <v>2784.5099</v>
+        <v>2784.51</v>
       </c>
       <c r="G129" s="8">
         <v>165</v>
@@ -13415,7 +13415,7 @@
         <v>3708</v>
       </c>
       <c r="F130" s="8">
-        <v>2136.744799999999</v>
+        <v>2136.7399999999998</v>
       </c>
       <c r="G130" s="8">
         <v>174</v>
@@ -13438,7 +13438,7 @@
         <v>14994</v>
       </c>
       <c r="F131" s="8">
-        <v>8914.8799000000035</v>
+        <v>8914.8799999999992</v>
       </c>
       <c r="G131" s="8">
         <v>168</v>
@@ -13461,7 +13461,7 @@
         <v>1842</v>
       </c>
       <c r="F132" s="8">
-        <v>2055.5908999999992</v>
+        <v>2055.59</v>
       </c>
       <c r="G132" s="8">
         <v>90</v>
@@ -13484,7 +13484,7 @@
         <v>3180</v>
       </c>
       <c r="F133" s="8">
-        <v>3139.934400000001</v>
+        <v>3139.93</v>
       </c>
       <c r="G133" s="8">
         <v>101</v>
@@ -13507,7 +13507,7 @@
         <v>3012</v>
       </c>
       <c r="F134" s="8">
-        <v>3054.3787000000011</v>
+        <v>3054.38</v>
       </c>
       <c r="G134" s="8">
         <v>99</v>
@@ -13530,7 +13530,7 @@
         <v>2052</v>
       </c>
       <c r="F135" s="8">
-        <v>1949.8107000000002</v>
+        <v>1949.81</v>
       </c>
       <c r="G135" s="8">
         <v>105</v>
@@ -13553,7 +13553,7 @@
         <v>14832</v>
       </c>
       <c r="F136" s="8">
-        <v>16815.83919999998</v>
+        <v>16815.84</v>
       </c>
       <c r="G136" s="8">
         <v>88</v>
@@ -13576,7 +13576,7 @@
         <v>726</v>
       </c>
       <c r="F137" s="8">
-        <v>732.87029999999993</v>
+        <v>732.87</v>
       </c>
       <c r="G137" s="8">
         <v>99</v>
@@ -13599,7 +13599,7 @@
         <v>10422</v>
       </c>
       <c r="F138" s="8">
-        <v>10373.833599999985</v>
+        <v>10373.83</v>
       </c>
       <c r="G138" s="8">
         <v>100</v>
@@ -13622,7 +13622,7 @@
         <v>7542</v>
       </c>
       <c r="F139" s="8">
-        <v>8072.8431000000073</v>
+        <v>8072.84</v>
       </c>
       <c r="G139" s="8">
         <v>93</v>
@@ -13645,7 +13645,7 @@
         <v>3690</v>
       </c>
       <c r="F140" s="8">
-        <v>3797.9258000000009</v>
+        <v>3797.93</v>
       </c>
       <c r="G140" s="8">
         <v>97</v>
@@ -13668,7 +13668,7 @@
         <v>20640</v>
       </c>
       <c r="F141" s="8">
-        <v>21615.598399999981</v>
+        <v>21615.599999999999</v>
       </c>
       <c r="G141" s="8">
         <v>95</v>
@@ -13691,7 +13691,7 @@
         <v>7392</v>
       </c>
       <c r="F142" s="8">
-        <v>25100.697899999966</v>
+        <v>25100.7</v>
       </c>
       <c r="G142" s="8">
         <v>28.999999999999996</v>
@@ -13714,7 +13714,7 @@
         <v>13812</v>
       </c>
       <c r="F143" s="8">
-        <v>42682.420299999991</v>
+        <v>42682.42</v>
       </c>
       <c r="G143" s="8">
         <v>32</v>
@@ -13737,7 +13737,7 @@
         <v>11982</v>
       </c>
       <c r="F144" s="8">
-        <v>40226.440299999987</v>
+        <v>40226.44</v>
       </c>
       <c r="G144" s="8">
         <v>30</v>
@@ -13760,7 +13760,7 @@
         <v>7074</v>
       </c>
       <c r="F145" s="8">
-        <v>23167.285800000027</v>
+        <v>23167.29</v>
       </c>
       <c r="G145" s="8">
         <v>31</v>
@@ -13783,7 +13783,7 @@
         <v>39594</v>
       </c>
       <c r="F146" s="8">
-        <v>136367.89060000001</v>
+        <v>136367.89000000001</v>
       </c>
       <c r="G146" s="8">
         <v>28.999999999999996</v>
@@ -13806,7 +13806,7 @@
         <v>3168</v>
       </c>
       <c r="F147" s="8">
-        <v>10919.091300000004</v>
+        <v>10919.09</v>
       </c>
       <c r="G147" s="8">
         <v>28.999999999999996</v>
@@ -13829,7 +13829,7 @@
         <v>26016</v>
       </c>
       <c r="F148" s="8">
-        <v>85316.020899999901</v>
+        <v>85316.02</v>
       </c>
       <c r="G148" s="8">
         <v>30</v>
@@ -13852,7 +13852,7 @@
         <v>14928</v>
       </c>
       <c r="F149" s="8">
-        <v>54078.107599999974</v>
+        <v>54078.11</v>
       </c>
       <c r="G149" s="8">
         <v>28.000000000000004</v>
@@ -13875,7 +13875,7 @@
         <v>17202</v>
       </c>
       <c r="F150" s="8">
-        <v>59071.614099999999</v>
+        <v>59071.61</v>
       </c>
       <c r="G150" s="8">
         <v>28.999999999999996</v>
@@ -13898,7 +13898,7 @@
         <v>65010</v>
       </c>
       <c r="F151" s="8">
-        <v>233979.85289999988</v>
+        <v>233979.85</v>
       </c>
       <c r="G151" s="8">
         <v>28.000000000000004</v>
@@ -13921,7 +13921,7 @@
         <v>162</v>
       </c>
       <c r="F152" s="8">
-        <v>34.721600000000002</v>
+        <v>34.72</v>
       </c>
       <c r="G152" s="8">
         <v>467</v>
@@ -13944,7 +13944,7 @@
         <v>336</v>
       </c>
       <c r="F153" s="8">
-        <v>77.703800000000015</v>
+        <v>77.7</v>
       </c>
       <c r="G153" s="8">
         <v>432</v>
@@ -13967,7 +13967,7 @@
         <v>270</v>
       </c>
       <c r="F154" s="8">
-        <v>76.885300000000001</v>
+        <v>76.89</v>
       </c>
       <c r="G154" s="8">
         <v>351</v>
@@ -13990,7 +13990,7 @@
         <v>162</v>
       </c>
       <c r="F155" s="8">
-        <v>35.576300000000003</v>
+        <v>35.58</v>
       </c>
       <c r="G155" s="8">
         <v>455</v>
@@ -14013,7 +14013,7 @@
         <v>906</v>
       </c>
       <c r="F156" s="8">
-        <v>186.30079999999998</v>
+        <v>186.3</v>
       </c>
       <c r="G156" s="8">
         <v>486.00000000000006</v>
@@ -14036,7 +14036,7 @@
         <v>204</v>
       </c>
       <c r="F157" s="8">
-        <v>42.484099999999998</v>
+        <v>42.48</v>
       </c>
       <c r="G157" s="8">
         <v>480</v>
@@ -14059,7 +14059,7 @@
         <v>270</v>
       </c>
       <c r="F158" s="8">
-        <v>132.87870000000001</v>
+        <v>132.88</v>
       </c>
       <c r="G158" s="8">
         <v>202.99999999999997</v>
@@ -14082,7 +14082,7 @@
         <v>276</v>
       </c>
       <c r="F159" s="8">
-        <v>62.040700000000015</v>
+        <v>62.04</v>
       </c>
       <c r="G159" s="8">
         <v>445</v>
@@ -14105,7 +14105,7 @@
         <v>204</v>
       </c>
       <c r="F160" s="8">
-        <v>72.390300000000025</v>
+        <v>72.39</v>
       </c>
       <c r="G160" s="8">
         <v>282</v>
@@ -14128,7 +14128,7 @@
         <v>1488</v>
       </c>
       <c r="F161" s="8">
-        <v>322.24559999999997</v>
+        <v>322.25</v>
       </c>
       <c r="G161" s="8">
         <v>462</v>
@@ -14151,7 +14151,7 @@
         <v>3360</v>
       </c>
       <c r="F162" s="8">
-        <v>2440.7151000000003</v>
+        <v>2440.7199999999998</v>
       </c>
       <c r="G162" s="8">
         <v>138</v>
@@ -14174,7 +14174,7 @@
         <v>4188</v>
       </c>
       <c r="F163" s="8">
-        <v>2541.1186999999982</v>
+        <v>2541.12</v>
       </c>
       <c r="G163" s="8">
         <v>165</v>
@@ -14197,7 +14197,7 @@
         <v>2298</v>
       </c>
       <c r="F164" s="8">
-        <v>1379.0413999999982</v>
+        <v>1379.04</v>
       </c>
       <c r="G164" s="8">
         <v>167</v>
@@ -14220,7 +14220,7 @@
         <v>2406</v>
       </c>
       <c r="F165" s="8">
-        <v>1452.1904999999997</v>
+        <v>1452.19</v>
       </c>
       <c r="G165" s="8">
         <v>166</v>
@@ -14243,7 +14243,7 @@
         <v>11694</v>
       </c>
       <c r="F166" s="8">
-        <v>6971.8639999999996</v>
+        <v>6971.86</v>
       </c>
       <c r="G166" s="8">
         <v>168</v>
@@ -14266,7 +14266,7 @@
         <v>1200</v>
       </c>
       <c r="F167" s="8">
-        <v>713.80309999999986</v>
+        <v>713.8</v>
       </c>
       <c r="G167" s="8">
         <v>168</v>
@@ -14289,7 +14289,7 @@
         <v>10680</v>
       </c>
       <c r="F168" s="8">
-        <v>6357.0765000000047</v>
+        <v>6357.08</v>
       </c>
       <c r="G168" s="8">
         <v>168</v>
@@ -14312,7 +14312,7 @@
         <v>9012</v>
       </c>
       <c r="F169" s="8">
-        <v>5735.7909000000036</v>
+        <v>5735.79</v>
       </c>
       <c r="G169" s="8">
         <v>157</v>
@@ -14335,7 +14335,7 @@
         <v>20436</v>
       </c>
       <c r="F170" s="8">
-        <v>12519.773100000006</v>
+        <v>12519.77</v>
       </c>
       <c r="G170" s="8">
         <v>163</v>
@@ -14358,7 +14358,7 @@
         <v>1890</v>
       </c>
       <c r="F171" s="8">
-        <v>2232.3667000000005</v>
+        <v>2232.37</v>
       </c>
       <c r="G171" s="8">
         <v>85</v>
@@ -14381,7 +14381,7 @@
         <v>3486</v>
       </c>
       <c r="F172" s="8">
-        <v>3569.6566000000003</v>
+        <v>3569.66</v>
       </c>
       <c r="G172" s="8">
         <v>98</v>
@@ -14404,7 +14404,7 @@
         <v>3558</v>
       </c>
       <c r="F173" s="8">
-        <v>3688.8212999999996</v>
+        <v>3688.82</v>
       </c>
       <c r="G173" s="8">
         <v>96</v>
@@ -14427,7 +14427,7 @@
         <v>2076</v>
       </c>
       <c r="F174" s="8">
-        <v>2115.6429999999996</v>
+        <v>2115.64</v>
       </c>
       <c r="G174" s="8">
         <v>98</v>
@@ -14450,7 +14450,7 @@
         <v>13230</v>
       </c>
       <c r="F175" s="8">
-        <v>15359.550100000011</v>
+        <v>15359.55</v>
       </c>
       <c r="G175" s="8">
         <v>86</v>
@@ -14473,7 +14473,7 @@
         <v>828</v>
       </c>
       <c r="F176" s="8">
-        <v>869.96669999999983</v>
+        <v>869.97</v>
       </c>
       <c r="G176" s="8">
         <v>95</v>
@@ -14496,7 +14496,7 @@
         <v>15756</v>
       </c>
       <c r="F177" s="8">
-        <v>18113.900300000001</v>
+        <v>18113.900000000001</v>
       </c>
       <c r="G177" s="8">
         <v>87</v>
@@ -14519,7 +14519,7 @@
         <v>9882</v>
       </c>
       <c r="F178" s="8">
-        <v>11781.75989999999</v>
+        <v>11781.76</v>
       </c>
       <c r="G178" s="8">
         <v>84</v>
@@ -14542,7 +14542,7 @@
         <v>24582</v>
       </c>
       <c r="F179" s="8">
-        <v>28468.9954</v>
+        <v>28469</v>
       </c>
       <c r="G179" s="8">
         <v>86</v>
@@ -14565,7 +14565,7 @@
         <v>9552</v>
       </c>
       <c r="F180" s="8">
-        <v>32934.926299999817</v>
+        <v>32934.93</v>
       </c>
       <c r="G180" s="8">
         <v>28.999999999999996</v>
@@ -14588,7 +14588,7 @@
         <v>17520</v>
       </c>
       <c r="F181" s="8">
-        <v>57986.867299999991</v>
+        <v>57986.87</v>
       </c>
       <c r="G181" s="8">
         <v>30</v>
@@ -14611,7 +14611,7 @@
         <v>13572</v>
       </c>
       <c r="F182" s="8">
-        <v>46724.093499999959</v>
+        <v>46724.09</v>
       </c>
       <c r="G182" s="8">
         <v>28.999999999999996</v>
@@ -14634,7 +14634,7 @@
         <v>7656</v>
       </c>
       <c r="F183" s="8">
-        <v>27270.366600000052</v>
+        <v>27270.37</v>
       </c>
       <c r="G183" s="8">
         <v>28.000000000000004</v>
@@ -14657,7 +14657,7 @@
         <v>40194</v>
       </c>
       <c r="F184" s="8">
-        <v>141486.09889999995</v>
+        <v>141486.1</v>
       </c>
       <c r="G184" s="8">
         <v>28.000000000000004</v>
@@ -14680,7 +14680,7 @@
         <v>4068</v>
       </c>
       <c r="F185" s="8">
-        <v>14549.105800000001</v>
+        <v>14549.11</v>
       </c>
       <c r="G185" s="8">
         <v>28.000000000000004</v>
@@ -14703,7 +14703,7 @@
         <v>26724</v>
       </c>
       <c r="F186" s="8">
-        <v>87990.10369999992</v>
+        <v>87990.1</v>
       </c>
       <c r="G186" s="8">
         <v>30</v>
@@ -14726,7 +14726,7 @@
         <v>21114</v>
       </c>
       <c r="F187" s="8">
-        <v>76722.731499999907</v>
+        <v>76722.73</v>
       </c>
       <c r="G187" s="8">
         <v>28.000000000000004</v>
@@ -14749,7 +14749,7 @@
         <v>73890</v>
       </c>
       <c r="F188" s="8">
-        <v>265620.57719999983</v>
+        <v>265620.58</v>
       </c>
       <c r="G188" s="8">
         <v>28.000000000000004</v>
@@ -14772,7 +14772,7 @@
         <v>204</v>
       </c>
       <c r="F189" s="8">
-        <v>78.637200000000007</v>
+        <v>78.64</v>
       </c>
       <c r="G189" s="8">
         <v>259</v>
@@ -14795,7 +14795,7 @@
         <v>414</v>
       </c>
       <c r="F190" s="8">
-        <v>97.425100000000015</v>
+        <v>97.43</v>
       </c>
       <c r="G190" s="8">
         <v>425</v>
@@ -14818,7 +14818,7 @@
         <v>240</v>
       </c>
       <c r="F191" s="8">
-        <v>80.514399999999995</v>
+        <v>80.510000000000005</v>
       </c>
       <c r="G191" s="8">
         <v>298</v>
@@ -14841,7 +14841,7 @@
         <v>222</v>
       </c>
       <c r="F192" s="8">
-        <v>54.152000000000001</v>
+        <v>54.15</v>
       </c>
       <c r="G192" s="8">
         <v>409.99999999999994</v>
@@ -14864,7 +14864,7 @@
         <v>1134</v>
       </c>
       <c r="F193" s="8">
-        <v>264.97660000000002</v>
+        <v>264.98</v>
       </c>
       <c r="G193" s="8">
         <v>428</v>
@@ -14887,7 +14887,7 @@
         <v>192</v>
       </c>
       <c r="F194" s="8">
-        <v>51.183999999999997</v>
+        <v>51.18</v>
       </c>
       <c r="G194" s="8">
         <v>375</v>
@@ -14910,7 +14910,7 @@
         <v>324</v>
       </c>
       <c r="F195" s="8">
-        <v>116.53120000000001</v>
+        <v>116.53</v>
       </c>
       <c r="G195" s="8">
         <v>278</v>
@@ -14933,7 +14933,7 @@
         <v>630</v>
       </c>
       <c r="F196" s="8">
-        <v>165.50149999999999</v>
+        <v>165.5</v>
       </c>
       <c r="G196" s="8">
         <v>381</v>
@@ -14956,7 +14956,7 @@
         <v>2718</v>
       </c>
       <c r="F197" s="8">
-        <v>612.14269999999988</v>
+        <v>612.14</v>
       </c>
       <c r="G197" s="8">
         <v>444.00000000000006</v>
@@ -14979,7 +14979,7 @@
         <v>3036</v>
       </c>
       <c r="F198" s="8">
-        <v>2224.609899999999</v>
+        <v>2224.61</v>
       </c>
       <c r="G198" s="8">
         <v>136</v>
@@ -15002,7 +15002,7 @@
         <v>3930</v>
       </c>
       <c r="F199" s="8">
-        <v>2464.8428000000004</v>
+        <v>2464.84</v>
       </c>
       <c r="G199" s="8">
         <v>159</v>
@@ -15025,7 +15025,7 @@
         <v>2646</v>
       </c>
       <c r="F200" s="8">
-        <v>1621.5290000000005</v>
+        <v>1621.53</v>
       </c>
       <c r="G200" s="8">
         <v>163</v>
@@ -15048,7 +15048,7 @@
         <v>2538</v>
       </c>
       <c r="F201" s="8">
-        <v>1558.912</v>
+        <v>1558.91</v>
       </c>
       <c r="G201" s="8">
         <v>163</v>
@@ -15071,7 +15071,7 @@
         <v>13284</v>
       </c>
       <c r="F202" s="8">
-        <v>8247.9119000000046</v>
+        <v>8247.91</v>
       </c>
       <c r="G202" s="8">
         <v>161</v>
@@ -15094,7 +15094,7 @@
         <v>2322</v>
       </c>
       <c r="F203" s="8">
-        <v>1713.7140999999999</v>
+        <v>1713.71</v>
       </c>
       <c r="G203" s="8">
         <v>135</v>
@@ -15117,7 +15117,7 @@
         <v>12444</v>
       </c>
       <c r="F204" s="8">
-        <v>7567.514500000003</v>
+        <v>7567.51</v>
       </c>
       <c r="G204" s="8">
         <v>164</v>
@@ -15140,7 +15140,7 @@
         <v>13290</v>
       </c>
       <c r="F205" s="8">
-        <v>9078.3615000000027</v>
+        <v>9078.36</v>
       </c>
       <c r="G205" s="8">
         <v>146</v>
@@ -15163,7 +15163,7 @@
         <v>6006</v>
       </c>
       <c r="F206" s="8">
-        <v>3648.4862000000012</v>
+        <v>3648.49</v>
       </c>
       <c r="G206" s="8">
         <v>165</v>
@@ -15186,7 +15186,7 @@
         <v>24210</v>
       </c>
       <c r="F207" s="8">
-        <v>15379.319</v>
+        <v>15379.32</v>
       </c>
       <c r="G207" s="8">
         <v>157</v>
@@ -15209,7 +15209,7 @@
         <v>1374</v>
       </c>
       <c r="F208" s="8">
-        <v>1647.3104999999987</v>
+        <v>1647.31</v>
       </c>
       <c r="G208" s="8">
         <v>83</v>
@@ -15232,7 +15232,7 @@
         <v>1614</v>
       </c>
       <c r="F209" s="8">
-        <v>1812.6783</v>
+        <v>1812.68</v>
       </c>
       <c r="G209" s="8">
         <v>89</v>
@@ -15255,7 +15255,7 @@
         <v>1746</v>
       </c>
       <c r="F210" s="8">
-        <v>1693.1128000000008</v>
+        <v>1693.11</v>
       </c>
       <c r="G210" s="8">
         <v>103</v>
@@ -15278,7 +15278,7 @@
         <v>1548</v>
       </c>
       <c r="F211" s="8">
-        <v>1545.2172000000005</v>
+        <v>1545.22</v>
       </c>
       <c r="G211" s="8">
         <v>100</v>
@@ -15301,7 +15301,7 @@
         <v>7734</v>
       </c>
       <c r="F212" s="8">
-        <v>9149.8546999999999</v>
+        <v>9149.85</v>
       </c>
       <c r="G212" s="8">
         <v>85</v>
@@ -15324,7 +15324,7 @@
         <v>762</v>
       </c>
       <c r="F213" s="8">
-        <v>751.08850000000029</v>
+        <v>751.09</v>
       </c>
       <c r="G213" s="8">
         <v>101</v>
@@ -15347,7 +15347,7 @@
         <v>7848</v>
       </c>
       <c r="F214" s="8">
-        <v>8961.7499999999945</v>
+        <v>8961.75</v>
       </c>
       <c r="G214" s="8">
         <v>88</v>
@@ -15370,7 +15370,7 @@
         <v>6498</v>
       </c>
       <c r="F215" s="8">
-        <v>7597.139699999997</v>
+        <v>7597.14</v>
       </c>
       <c r="G215" s="8">
         <v>86</v>
@@ -15393,7 +15393,7 @@
         <v>2592</v>
       </c>
       <c r="F216" s="8">
-        <v>3198.2575000000006</v>
+        <v>3198.26</v>
       </c>
       <c r="G216" s="8">
         <v>81</v>
@@ -15416,7 +15416,7 @@
         <v>21324</v>
       </c>
       <c r="F217" s="8">
-        <v>26453.411399999997</v>
+        <v>26453.41</v>
       </c>
       <c r="G217" s="8">
         <v>81</v>
@@ -15439,7 +15439,7 @@
         <v>10062</v>
       </c>
       <c r="F218" s="8">
-        <v>34601.206200000139</v>
+        <v>34601.21</v>
       </c>
       <c r="G218" s="8">
         <v>28.999999999999996</v>
@@ -15462,7 +15462,7 @@
         <v>17364</v>
       </c>
       <c r="F219" s="8">
-        <v>57162.663200000054</v>
+        <v>57162.66</v>
       </c>
       <c r="G219" s="8">
         <v>30</v>
@@ -15485,7 +15485,7 @@
         <v>13356</v>
       </c>
       <c r="F220" s="8">
-        <v>46311.703900000022</v>
+        <v>46311.7</v>
       </c>
       <c r="G220" s="8">
         <v>28.999999999999996</v>
@@ -15508,7 +15508,7 @@
         <v>8706</v>
       </c>
       <c r="F221" s="8">
-        <v>30889.652599999994</v>
+        <v>30889.65</v>
       </c>
       <c r="G221" s="8">
         <v>28.000000000000004</v>
@@ -15531,7 +15531,7 @@
         <v>37482</v>
       </c>
       <c r="F222" s="8">
-        <v>134042.80190000025</v>
+        <v>134042.79999999999</v>
       </c>
       <c r="G222" s="8">
         <v>28.000000000000004</v>
@@ -15554,7 +15554,7 @@
         <v>5412</v>
       </c>
       <c r="F223" s="8">
-        <v>16134.785399999995</v>
+        <v>16134.79</v>
       </c>
       <c r="G223" s="8">
         <v>34</v>
@@ -15577,7 +15577,7 @@
         <v>33492</v>
       </c>
       <c r="F224" s="8">
-        <v>119035.32220000001</v>
+        <v>119035.32</v>
       </c>
       <c r="G224" s="8">
         <v>28.000000000000004</v>
@@ -15600,7 +15600,7 @@
         <v>26340</v>
       </c>
       <c r="F225" s="8">
-        <v>99098.482600000076</v>
+        <v>99098.48</v>
       </c>
       <c r="G225" s="8">
         <v>27</v>
@@ -15623,7 +15623,7 @@
         <v>23022</v>
       </c>
       <c r="F226" s="8">
-        <v>82537.262600000045</v>
+        <v>82537.259999999995</v>
       </c>
       <c r="G226" s="8">
         <v>28.000000000000004</v>
@@ -15646,7 +15646,7 @@
         <v>86064</v>
       </c>
       <c r="F227" s="8">
-        <v>322324.80779999937</v>
+        <v>322324.81</v>
       </c>
       <c r="G227" s="8">
         <v>27</v>
@@ -15669,7 +15669,7 @@
         <v>204</v>
       </c>
       <c r="F228" s="8">
-        <v>69.5107</v>
+        <v>69.510000000000005</v>
       </c>
       <c r="G228" s="8">
         <v>293</v>
@@ -15692,7 +15692,7 @@
         <v>354</v>
       </c>
       <c r="F229" s="8">
-        <v>100.60839999999999</v>
+        <v>100.61</v>
       </c>
       <c r="G229" s="8">
         <v>352</v>
@@ -15715,7 +15715,7 @@
         <v>312</v>
       </c>
       <c r="F230" s="8">
-        <v>110.60319999999999</v>
+        <v>110.6</v>
       </c>
       <c r="G230" s="8">
         <v>282</v>
@@ -15738,7 +15738,7 @@
         <v>198</v>
       </c>
       <c r="F231" s="8">
-        <v>57.159400000000005</v>
+        <v>57.16</v>
       </c>
       <c r="G231" s="8">
         <v>346</v>
@@ -15761,7 +15761,7 @@
         <v>780</v>
       </c>
       <c r="F232" s="8">
-        <v>186.5788</v>
+        <v>186.58</v>
       </c>
       <c r="G232" s="8">
         <v>418</v>
@@ -15784,7 +15784,7 @@
         <v>78</v>
       </c>
       <c r="F233" s="8">
-        <v>20.280900000000003</v>
+        <v>20.28</v>
       </c>
       <c r="G233" s="8">
         <v>385</v>
@@ -15807,7 +15807,7 @@
         <v>306</v>
       </c>
       <c r="F234" s="8">
-        <v>90.868700000000018</v>
+        <v>90.87</v>
       </c>
       <c r="G234" s="8">
         <v>337</v>
@@ -15830,7 +15830,7 @@
         <v>294</v>
       </c>
       <c r="F235" s="8">
-        <v>102.63400000000001</v>
+        <v>102.63</v>
       </c>
       <c r="G235" s="8">
         <v>286</v>
@@ -15853,7 +15853,7 @@
         <v>264</v>
       </c>
       <c r="F236" s="8">
-        <v>84.323000000000008</v>
+        <v>84.32</v>
       </c>
       <c r="G236" s="8">
         <v>313</v>
@@ -15876,7 +15876,7 @@
         <v>2586</v>
       </c>
       <c r="F237" s="8">
-        <v>584.36520000000007</v>
+        <v>584.37</v>
       </c>
       <c r="G237" s="8">
         <v>443</v>
@@ -15899,7 +15899,7 @@
         <v>348</v>
       </c>
       <c r="F238" s="5">
-        <v>198.37990000000002</v>
+        <v>198.38</v>
       </c>
       <c r="G238" s="21">
         <v>175</v>
@@ -15922,7 +15922,7 @@
         <v>984</v>
       </c>
       <c r="F239" s="8">
-        <v>505.63960000000031</v>
+        <v>505.64</v>
       </c>
       <c r="G239" s="22">
         <v>195</v>
@@ -15945,7 +15945,7 @@
         <v>618</v>
       </c>
       <c r="F240" s="8">
-        <v>342.79800000000017</v>
+        <v>342.8</v>
       </c>
       <c r="G240" s="22">
         <v>180</v>
@@ -15968,7 +15968,7 @@
         <v>408</v>
       </c>
       <c r="F241" s="8">
-        <v>210.32919999999999</v>
+        <v>210.33</v>
       </c>
       <c r="G241" s="22">
         <v>194</v>
@@ -15991,7 +15991,7 @@
         <v>3792</v>
       </c>
       <c r="F242" s="8">
-        <v>1932.4755000000018</v>
+        <v>1932.48</v>
       </c>
       <c r="G242" s="22">
         <v>196</v>
@@ -16014,7 +16014,7 @@
         <v>234</v>
       </c>
       <c r="F243" s="8">
-        <v>114.50350000000003</v>
+        <v>114.5</v>
       </c>
       <c r="G243" s="22">
         <v>204</v>
@@ -16037,7 +16037,7 @@
         <v>1656</v>
       </c>
       <c r="F244" s="8">
-        <v>827.94499999999937</v>
+        <v>827.94</v>
       </c>
       <c r="G244" s="22">
         <v>200</v>
@@ -16060,7 +16060,7 @@
         <v>1086</v>
       </c>
       <c r="F245" s="8">
-        <v>570.08900000000028</v>
+        <v>570.09</v>
       </c>
       <c r="G245" s="22">
         <v>190</v>
@@ -16083,7 +16083,7 @@
         <v>726</v>
       </c>
       <c r="F246" s="8">
-        <v>367.43020000000013</v>
+        <v>367.43</v>
       </c>
       <c r="G246" s="22">
         <v>198</v>
@@ -16106,7 +16106,7 @@
         <v>3222</v>
       </c>
       <c r="F247" s="8">
-        <v>1624.1678000000009</v>
+        <v>1624.17</v>
       </c>
       <c r="G247" s="22">
         <v>198</v>
@@ -16129,7 +16129,7 @@
         <v>180</v>
       </c>
       <c r="F248" s="8">
-        <v>175.96120000000005</v>
+        <v>175.96</v>
       </c>
       <c r="G248" s="22">
         <v>102</v>
@@ -16152,7 +16152,7 @@
         <v>1182</v>
       </c>
       <c r="F249" s="8">
-        <v>1136.3918999999999</v>
+        <v>1136.3900000000001</v>
       </c>
       <c r="G249" s="22">
         <v>104</v>
@@ -16175,7 +16175,7 @@
         <v>1296</v>
       </c>
       <c r="F250" s="8">
-        <v>1198.4144999999996</v>
+        <v>1198.4100000000001</v>
       </c>
       <c r="G250" s="22">
         <v>108</v>
@@ -16198,7 +16198,7 @@
         <v>690</v>
       </c>
       <c r="F251" s="8">
-        <v>544.28859999999986</v>
+        <v>544.29</v>
       </c>
       <c r="G251" s="22">
         <v>127</v>
@@ -16221,7 +16221,7 @@
         <v>9780</v>
       </c>
       <c r="F252" s="8">
-        <v>10201.448800000013</v>
+        <v>10201.450000000001</v>
       </c>
       <c r="G252" s="22">
         <v>96</v>
@@ -16244,7 +16244,7 @@
         <v>204</v>
       </c>
       <c r="F253" s="8">
-        <v>180.2732</v>
+        <v>180.27</v>
       </c>
       <c r="G253" s="22">
         <v>112.99999999999999</v>
@@ -16267,7 +16267,7 @@
         <v>3150</v>
       </c>
       <c r="F254" s="8">
-        <v>2568.789400000001</v>
+        <v>2568.79</v>
       </c>
       <c r="G254" s="22">
         <v>123</v>
@@ -16290,7 +16290,7 @@
         <v>1734</v>
       </c>
       <c r="F255" s="8">
-        <v>1791.7562999999996</v>
+        <v>1791.76</v>
       </c>
       <c r="G255" s="22">
         <v>97</v>
@@ -16313,7 +16313,7 @@
         <v>1278</v>
       </c>
       <c r="F256" s="8">
-        <v>1119.0870999999995</v>
+        <v>1119.0899999999999</v>
       </c>
       <c r="G256" s="22">
         <v>113.99999999999999</v>
@@ -16336,7 +16336,7 @@
         <v>5994</v>
       </c>
       <c r="F257" s="8">
-        <v>5874.4116999999987</v>
+        <v>5874.41</v>
       </c>
       <c r="G257" s="22">
         <v>102</v>
@@ -16359,7 +16359,7 @@
         <v>540</v>
       </c>
       <c r="F258" s="8">
-        <v>1667.2467000000013</v>
+        <v>1667.25</v>
       </c>
       <c r="G258" s="22">
         <v>32</v>
@@ -16382,7 +16382,7 @@
         <v>2274</v>
       </c>
       <c r="F259" s="8">
-        <v>7772.1337999999951</v>
+        <v>7772.13</v>
       </c>
       <c r="G259" s="22">
         <v>28.999999999999996</v>
@@ -16405,7 +16405,7 @@
         <v>2058</v>
       </c>
       <c r="F260" s="8">
-        <v>7190.1295999999993</v>
+        <v>7190.13</v>
       </c>
       <c r="G260" s="22">
         <v>28.999999999999996</v>
@@ -16428,7 +16428,7 @@
         <v>1638</v>
       </c>
       <c r="F261" s="8">
-        <v>5569.0451999999923</v>
+        <v>5569.05</v>
       </c>
       <c r="G261" s="22">
         <v>28.999999999999996</v>
@@ -16451,7 +16451,7 @@
         <v>12348</v>
       </c>
       <c r="F262" s="8">
-        <v>41748.29760000002</v>
+        <v>41748.300000000003</v>
       </c>
       <c r="G262" s="22">
         <v>30</v>
@@ -16474,7 +16474,7 @@
         <v>456</v>
       </c>
       <c r="F263" s="8">
-        <v>1594.2984000000006</v>
+        <v>1594.3</v>
       </c>
       <c r="G263" s="22">
         <v>28.999999999999996</v>
@@ -16497,7 +16497,7 @@
         <v>4662</v>
       </c>
       <c r="F264" s="8">
-        <v>16444.666599999997</v>
+        <v>16444.669999999998</v>
       </c>
       <c r="G264" s="22">
         <v>28.000000000000004</v>
@@ -16520,7 +16520,7 @@
         <v>2742</v>
       </c>
       <c r="F265" s="8">
-        <v>9644.4929999999949</v>
+        <v>9644.49</v>
       </c>
       <c r="G265" s="22">
         <v>28.000000000000004</v>
@@ -16543,7 +16543,7 @@
         <v>4170</v>
       </c>
       <c r="F266" s="8">
-        <v>14969.335799999997</v>
+        <v>14969.34</v>
       </c>
       <c r="G266" s="22">
         <v>28.000000000000004</v>
@@ -16566,7 +16566,7 @@
         <v>14682</v>
       </c>
       <c r="F267" s="8">
-        <v>52326.60550000002</v>
+        <v>52326.61</v>
       </c>
       <c r="G267" s="22">
         <v>28.000000000000004</v>
@@ -16589,7 +16589,7 @@
         <v>24</v>
       </c>
       <c r="F268" s="8">
-        <v>5.8548999999999998</v>
+        <v>5.85</v>
       </c>
       <c r="G268" s="22">
         <v>409.99999999999994</v>
@@ -16612,7 +16612,7 @@
         <v>42</v>
       </c>
       <c r="F269" s="8">
-        <v>14.165099999999999</v>
+        <v>14.17</v>
       </c>
       <c r="G269" s="22">
         <v>297</v>
@@ -16635,7 +16635,7 @@
         <v>66</v>
       </c>
       <c r="F270" s="8">
-        <v>25.3566</v>
+        <v>25.36</v>
       </c>
       <c r="G270" s="22">
         <v>260</v>
@@ -16658,7 +16658,7 @@
         <v>36</v>
       </c>
       <c r="F271" s="8">
-        <v>8.3560999999999996</v>
+        <v>8.36</v>
       </c>
       <c r="G271" s="22">
         <v>430.99999999999994</v>
@@ -16681,7 +16681,7 @@
         <v>156</v>
       </c>
       <c r="F272" s="8">
-        <v>58.977000000000004</v>
+        <v>58.98</v>
       </c>
       <c r="G272" s="22">
         <v>265</v>
@@ -16704,7 +16704,7 @@
         <v>36</v>
       </c>
       <c r="F273" s="8">
-        <v>10.765000000000001</v>
+        <v>10.77</v>
       </c>
       <c r="G273" s="22">
         <v>334</v>
@@ -16727,7 +16727,7 @@
         <v>96</v>
       </c>
       <c r="F274" s="8">
-        <v>39.9482</v>
+        <v>39.950000000000003</v>
       </c>
       <c r="G274" s="22">
         <v>240</v>
@@ -16750,7 +16750,7 @@
         <v>156</v>
       </c>
       <c r="F275" s="8">
-        <v>49.860199999999999</v>
+        <v>49.86</v>
       </c>
       <c r="G275" s="22">
         <v>313</v>
@@ -16773,7 +16773,7 @@
         <v>30</v>
       </c>
       <c r="F276" s="8">
-        <v>6.3273000000000001</v>
+        <v>6.33</v>
       </c>
       <c r="G276" s="22">
         <v>474</v>
@@ -16796,7 +16796,7 @@
         <v>330</v>
       </c>
       <c r="F277" s="8">
-        <v>118.51870000000005</v>
+        <v>118.52</v>
       </c>
       <c r="G277" s="22">
         <v>278</v>
@@ -16819,7 +16819,7 @@
         <v>504</v>
       </c>
       <c r="F278" s="8">
-        <v>301.82740000000001</v>
+        <v>301.83</v>
       </c>
       <c r="G278" s="22">
         <v>167</v>
@@ -16842,7 +16842,7 @@
         <v>1674</v>
       </c>
       <c r="F279" s="8">
-        <v>935.71810000000005</v>
+        <v>935.72</v>
       </c>
       <c r="G279" s="22">
         <v>179</v>
@@ -16865,7 +16865,7 @@
         <v>702</v>
       </c>
       <c r="F280" s="8">
-        <v>390.63489999999985</v>
+        <v>390.63</v>
       </c>
       <c r="G280" s="22">
         <v>180</v>
@@ -16888,7 +16888,7 @@
         <v>828</v>
       </c>
       <c r="F281" s="8">
-        <v>429.19380000000001</v>
+        <v>429.19</v>
       </c>
       <c r="G281" s="22">
         <v>193</v>
@@ -16911,7 +16911,7 @@
         <v>5748</v>
       </c>
       <c r="F282" s="8">
-        <v>3219.1460999999954</v>
+        <v>3219.15</v>
       </c>
       <c r="G282" s="22">
         <v>179</v>
@@ -16934,7 +16934,7 @@
         <v>210</v>
       </c>
       <c r="F283" s="8">
-        <v>105.50719999999998</v>
+        <v>105.51</v>
       </c>
       <c r="G283" s="22">
         <v>199</v>
@@ -16957,7 +16957,7 @@
         <v>2502</v>
       </c>
       <c r="F284" s="8">
-        <v>1321.6353999999997</v>
+        <v>1321.64</v>
       </c>
       <c r="G284" s="22">
         <v>189</v>
@@ -16980,7 +16980,7 @@
         <v>1836</v>
       </c>
       <c r="F285" s="8">
-        <v>1073.0859</v>
+        <v>1073.0899999999999</v>
       </c>
       <c r="G285" s="22">
         <v>171</v>
@@ -17003,7 +17003,7 @@
         <v>1194</v>
       </c>
       <c r="F286" s="8">
-        <v>666.18150000000014</v>
+        <v>666.18</v>
       </c>
       <c r="G286" s="22">
         <v>179</v>
@@ -17026,7 +17026,7 @@
         <v>6018</v>
       </c>
       <c r="F287" s="8">
-        <v>3243.1953999999978</v>
+        <v>3243.2</v>
       </c>
       <c r="G287" s="22">
         <v>186</v>
@@ -17049,7 +17049,7 @@
         <v>414</v>
       </c>
       <c r="F288" s="8">
-        <v>377.8099000000002</v>
+        <v>377.81</v>
       </c>
       <c r="G288" s="22">
         <v>110.00000000000001</v>
@@ -17072,7 +17072,7 @@
         <v>1578</v>
       </c>
       <c r="F289" s="8">
-        <v>1550.3152000000014</v>
+        <v>1550.32</v>
       </c>
       <c r="G289" s="22">
         <v>102</v>
@@ -17095,7 +17095,7 @@
         <v>2220</v>
       </c>
       <c r="F290" s="8">
-        <v>2082.9980000000028</v>
+        <v>2083</v>
       </c>
       <c r="G290" s="22">
         <v>107</v>
@@ -17118,7 +17118,7 @@
         <v>792</v>
       </c>
       <c r="F291" s="8">
-        <v>543.62930000000017</v>
+        <v>543.63</v>
       </c>
       <c r="G291" s="22">
         <v>146</v>
@@ -17141,7 +17141,7 @@
         <v>13596</v>
       </c>
       <c r="F292" s="8">
-        <v>13787.52519999998</v>
+        <v>13787.53</v>
       </c>
       <c r="G292" s="22">
         <v>99</v>
@@ -17164,7 +17164,7 @@
         <v>426</v>
       </c>
       <c r="F293" s="8">
-        <v>367.94990000000013</v>
+        <v>367.95</v>
       </c>
       <c r="G293" s="22">
         <v>115.99999999999999</v>
@@ -17187,7 +17187,7 @@
         <v>4722</v>
       </c>
       <c r="F294" s="8">
-        <v>4272.2646000000041</v>
+        <v>4272.26</v>
       </c>
       <c r="G294" s="22">
         <v>111.00000000000001</v>
@@ -17210,7 +17210,7 @@
         <v>3822</v>
       </c>
       <c r="F295" s="8">
-        <v>3989.4864000000052</v>
+        <v>3989.49</v>
       </c>
       <c r="G295" s="22">
         <v>96</v>
@@ -17233,7 +17233,7 @@
         <v>2016</v>
       </c>
       <c r="F296" s="8">
-        <v>1890.5486000000008</v>
+        <v>1890.55</v>
       </c>
       <c r="G296" s="22">
         <v>107</v>
@@ -17256,7 +17256,7 @@
         <v>9882</v>
       </c>
       <c r="F297" s="8">
-        <v>9397.2748999999931</v>
+        <v>9397.27</v>
       </c>
       <c r="G297" s="22">
         <v>105</v>
@@ -17279,7 +17279,7 @@
         <v>2406</v>
       </c>
       <c r="F298" s="8">
-        <v>7851.3946000000124</v>
+        <v>7851.39</v>
       </c>
       <c r="G298" s="22">
         <v>31</v>
@@ -17302,7 +17302,7 @@
         <v>6450</v>
       </c>
       <c r="F299" s="8">
-        <v>19838.276300000001</v>
+        <v>19838.28</v>
       </c>
       <c r="G299" s="22">
         <v>33</v>
@@ -17325,7 +17325,7 @@
         <v>6918</v>
       </c>
       <c r="F300" s="8">
-        <v>22091.477999999996</v>
+        <v>22091.48</v>
       </c>
       <c r="G300" s="22">
         <v>31</v>
@@ -17348,7 +17348,7 @@
         <v>3108</v>
       </c>
       <c r="F301" s="8">
-        <v>9997.6930000000102</v>
+        <v>9997.69</v>
       </c>
       <c r="G301" s="22">
         <v>31</v>
@@ -17371,7 +17371,7 @@
         <v>29976</v>
       </c>
       <c r="F302" s="8">
-        <v>99609.870999999985</v>
+        <v>99609.87</v>
       </c>
       <c r="G302" s="22">
         <v>30</v>
@@ -17394,7 +17394,7 @@
         <v>1410</v>
       </c>
       <c r="F303" s="8">
-        <v>4212.0717000000031</v>
+        <v>4212.07</v>
       </c>
       <c r="G303" s="22">
         <v>33</v>
@@ -17417,7 +17417,7 @@
         <v>12096</v>
       </c>
       <c r="F304" s="8">
-        <v>41099.141399999979</v>
+        <v>41099.14</v>
       </c>
       <c r="G304" s="22">
         <v>28.999999999999996</v>
@@ -17440,7 +17440,7 @@
         <v>7632</v>
       </c>
       <c r="F305" s="8">
-        <v>26076.756100000017</v>
+        <v>26076.76</v>
       </c>
       <c r="G305" s="22">
         <v>28.999999999999996</v>
@@ -17463,7 +17463,7 @@
         <v>9030</v>
       </c>
       <c r="F306" s="8">
-        <v>30052.045699999995</v>
+        <v>30052.05</v>
       </c>
       <c r="G306" s="22">
         <v>30</v>
@@ -17486,7 +17486,7 @@
         <v>32376</v>
       </c>
       <c r="F307" s="8">
-        <v>111415.51629999992</v>
+        <v>111415.52</v>
       </c>
       <c r="G307" s="22">
         <v>28.999999999999996</v>
@@ -17509,7 +17509,7 @@
         <v>54</v>
       </c>
       <c r="F308" s="8">
-        <v>16.584600000000002</v>
+        <v>16.579999999999998</v>
       </c>
       <c r="G308" s="22">
         <v>326</v>
@@ -17532,7 +17532,7 @@
         <v>66</v>
       </c>
       <c r="F309" s="8">
-        <v>14.397400000000001</v>
+        <v>14.4</v>
       </c>
       <c r="G309" s="22">
         <v>458</v>
@@ -17555,7 +17555,7 @@
         <v>150</v>
       </c>
       <c r="F310" s="8">
-        <v>35.357999999999997</v>
+        <v>35.36</v>
       </c>
       <c r="G310" s="22">
         <v>424</v>
@@ -17578,7 +17578,7 @@
         <v>108</v>
       </c>
       <c r="F311" s="8">
-        <v>22.541999999999998</v>
+        <v>22.54</v>
       </c>
       <c r="G311" s="22">
         <v>479</v>
@@ -17601,7 +17601,7 @@
         <v>576</v>
       </c>
       <c r="F312" s="8">
-        <v>132.06010000000009</v>
+        <v>132.06</v>
       </c>
       <c r="G312" s="22">
         <v>436.00000000000006</v>
@@ -17624,7 +17624,7 @@
         <v>66</v>
       </c>
       <c r="F313" s="8">
-        <v>12.840300000000001</v>
+        <v>12.84</v>
       </c>
       <c r="G313" s="22">
         <v>514</v>
@@ -17647,7 +17647,7 @@
         <v>168</v>
       </c>
       <c r="F314" s="8">
-        <v>73.543899999999994</v>
+        <v>73.540000000000006</v>
       </c>
       <c r="G314" s="22">
         <v>227.99999999999997</v>
@@ -17670,7 +17670,7 @@
         <v>450</v>
       </c>
       <c r="F315" s="8">
-        <v>94.143900000000087</v>
+        <v>94.14</v>
       </c>
       <c r="G315" s="22">
         <v>478</v>
@@ -17693,7 +17693,7 @@
         <v>96</v>
       </c>
       <c r="F316" s="8">
-        <v>16.1813</v>
+        <v>16.18</v>
       </c>
       <c r="G316" s="22">
         <v>593</v>
@@ -17716,7 +17716,7 @@
         <v>744</v>
       </c>
       <c r="F317" s="8">
-        <v>168.79270000000005</v>
+        <v>168.79</v>
       </c>
       <c r="G317" s="22">
         <v>441</v>
@@ -17739,7 +17739,7 @@
         <v>354</v>
       </c>
       <c r="F318" s="8">
-        <v>235.4900999999999</v>
+        <v>235.49</v>
       </c>
       <c r="G318" s="22">
         <v>150</v>
@@ -17762,7 +17762,7 @@
         <v>1260</v>
       </c>
       <c r="F319" s="8">
-        <v>683.55760000000032</v>
+        <v>683.56</v>
       </c>
       <c r="G319" s="22">
         <v>184</v>
@@ -17785,7 +17785,7 @@
         <v>468</v>
       </c>
       <c r="F320" s="8">
-        <v>259.77800000000002</v>
+        <v>259.77999999999997</v>
       </c>
       <c r="G320" s="22">
         <v>180</v>
@@ -17808,7 +17808,7 @@
         <v>540</v>
       </c>
       <c r="F321" s="8">
-        <v>278.51130000000001</v>
+        <v>278.51</v>
       </c>
       <c r="G321" s="22">
         <v>194</v>
@@ -17831,7 +17831,7 @@
         <v>4110</v>
       </c>
       <c r="F322" s="8">
-        <v>2337.6597999999976</v>
+        <v>2337.66</v>
       </c>
       <c r="G322" s="22">
         <v>176</v>
@@ -17854,7 +17854,7 @@
         <v>240</v>
       </c>
       <c r="F323" s="8">
-        <v>137.51539999999997</v>
+        <v>137.52000000000001</v>
       </c>
       <c r="G323" s="22">
         <v>175</v>
@@ -17877,7 +17877,7 @@
         <v>1398</v>
       </c>
       <c r="F324" s="8">
-        <v>745.72390000000041</v>
+        <v>745.72</v>
       </c>
       <c r="G324" s="22">
         <v>187</v>
@@ -17900,7 +17900,7 @@
         <v>1026</v>
       </c>
       <c r="F325" s="8">
-        <v>620.07610000000011</v>
+        <v>620.08000000000004</v>
       </c>
       <c r="G325" s="22">
         <v>165</v>
@@ -17923,7 +17923,7 @@
         <v>1302</v>
       </c>
       <c r="F326" s="8">
-        <v>757.75069999999994</v>
+        <v>757.75</v>
       </c>
       <c r="G326" s="22">
         <v>172</v>
@@ -17946,7 +17946,7 @@
         <v>6504</v>
       </c>
       <c r="F327" s="8">
-        <v>3768.7296999999999</v>
+        <v>3768.73</v>
       </c>
       <c r="G327" s="22">
         <v>173</v>
@@ -17969,7 +17969,7 @@
         <v>216</v>
       </c>
       <c r="F328" s="8">
-        <v>259.90970000000004</v>
+        <v>259.91000000000003</v>
       </c>
       <c r="G328" s="22">
         <v>83</v>
@@ -17992,7 +17992,7 @@
         <v>618</v>
       </c>
       <c r="F329" s="8">
-        <v>681.51560000000018</v>
+        <v>681.52</v>
       </c>
       <c r="G329" s="22">
         <v>91</v>
@@ -18015,7 +18015,7 @@
         <v>504</v>
       </c>
       <c r="F330" s="8">
-        <v>543.51149999999984</v>
+        <v>543.51</v>
       </c>
       <c r="G330" s="22">
         <v>93</v>
@@ -18038,7 +18038,7 @@
         <v>420</v>
       </c>
       <c r="F331" s="8">
-        <v>328.97620000000001</v>
+        <v>328.98</v>
       </c>
       <c r="G331" s="22">
         <v>128</v>
@@ -18061,7 +18061,7 @@
         <v>6552</v>
       </c>
       <c r="F332" s="8">
-        <v>7755.4854999999807</v>
+        <v>7755.49</v>
       </c>
       <c r="G332" s="22">
         <v>84</v>
@@ -18084,7 +18084,7 @@
         <v>138</v>
       </c>
       <c r="F333" s="8">
-        <v>143.43770000000001</v>
+        <v>143.44</v>
       </c>
       <c r="G333" s="22">
         <v>96</v>
@@ -18107,7 +18107,7 @@
         <v>1674</v>
       </c>
       <c r="F334" s="8">
-        <v>1619.9286000000006</v>
+        <v>1619.93</v>
       </c>
       <c r="G334" s="22">
         <v>103</v>
@@ -18130,7 +18130,7 @@
         <v>1134</v>
       </c>
       <c r="F335" s="8">
-        <v>1278.5514000000001</v>
+        <v>1278.55</v>
       </c>
       <c r="G335" s="22">
         <v>89</v>
@@ -18153,7 +18153,7 @@
         <v>954</v>
       </c>
       <c r="F336" s="8">
-        <v>1049.4199999999998</v>
+        <v>1049.42</v>
       </c>
       <c r="G336" s="22">
         <v>91</v>
@@ -18176,7 +18176,7 @@
         <v>6546</v>
       </c>
       <c r="F337" s="8">
-        <v>6641.9066999999877</v>
+        <v>6641.91</v>
       </c>
       <c r="G337" s="22">
         <v>99</v>
@@ -18199,7 +18199,7 @@
         <v>2490</v>
       </c>
       <c r="F338" s="8">
-        <v>8217.5519000000004</v>
+        <v>8217.5499999999993</v>
       </c>
       <c r="G338" s="22">
         <v>30</v>
@@ -18222,7 +18222,7 @@
         <v>6714</v>
       </c>
       <c r="F339" s="8">
-        <v>20166.598799999952</v>
+        <v>20166.599999999999</v>
       </c>
       <c r="G339" s="22">
         <v>33</v>
@@ -18245,7 +18245,7 @@
         <v>5004</v>
       </c>
       <c r="F340" s="8">
-        <v>16234.300099999986</v>
+        <v>16234.3</v>
       </c>
       <c r="G340" s="22">
         <v>31</v>
@@ -18268,7 +18268,7 @@
         <v>2076</v>
       </c>
       <c r="F341" s="8">
-        <v>6779.7257000000127</v>
+        <v>6779.73</v>
       </c>
       <c r="G341" s="22">
         <v>31</v>
@@ -18291,7 +18291,7 @@
         <v>25926</v>
       </c>
       <c r="F342" s="8">
-        <v>85118.320000000065</v>
+        <v>85118.32</v>
       </c>
       <c r="G342" s="22">
         <v>30</v>
@@ -18314,7 +18314,7 @@
         <v>1254</v>
       </c>
       <c r="F343" s="8">
-        <v>3803.7574000000013</v>
+        <v>3803.76</v>
       </c>
       <c r="G343" s="22">
         <v>33</v>
@@ -18337,7 +18337,7 @@
         <v>6696</v>
       </c>
       <c r="F344" s="8">
-        <v>24034.162699999964</v>
+        <v>24034.16</v>
       </c>
       <c r="G344" s="22">
         <v>28.000000000000004</v>
@@ -18360,7 +18360,7 @@
         <v>4338</v>
       </c>
       <c r="F345" s="8">
-        <v>14943.779899999992</v>
+        <v>14943.78</v>
       </c>
       <c r="G345" s="22">
         <v>28.999999999999996</v>
@@ -18383,7 +18383,7 @@
         <v>8784</v>
       </c>
       <c r="F346" s="8">
-        <v>32544.275599999964</v>
+        <v>32544.28</v>
       </c>
       <c r="G346" s="22">
         <v>27</v>
@@ -18406,7 +18406,7 @@
         <v>32946</v>
       </c>
       <c r="F347" s="8">
-        <v>115600.13130000002</v>
+        <v>115600.13</v>
       </c>
       <c r="G347" s="22">
         <v>28.000000000000004</v>
@@ -18429,7 +18429,7 @@
         <v>66</v>
       </c>
       <c r="F348" s="8">
-        <v>16.158099999999997</v>
+        <v>16.16</v>
       </c>
       <c r="G348" s="22">
         <v>408</v>
@@ -18452,7 +18452,7 @@
         <v>156</v>
       </c>
       <c r="F349" s="8">
-        <v>31.0472</v>
+        <v>31.05</v>
       </c>
       <c r="G349" s="22">
         <v>501.99999999999994</v>
@@ -18475,7 +18475,7 @@
         <v>126</v>
       </c>
       <c r="F350" s="8">
-        <v>36.9129</v>
+        <v>36.909999999999997</v>
       </c>
       <c r="G350" s="22">
         <v>341</v>
@@ -18498,7 +18498,7 @@
         <v>108</v>
       </c>
       <c r="F351" s="8">
-        <v>15.798199999999998</v>
+        <v>15.8</v>
       </c>
       <c r="G351" s="22">
         <v>684</v>
@@ -18521,7 +18521,7 @@
         <v>462</v>
       </c>
       <c r="F352" s="8">
-        <v>99.65319999999997</v>
+        <v>99.65</v>
       </c>
       <c r="G352" s="22">
         <v>463.99999999999994</v>
@@ -18544,7 +18544,7 @@
         <v>132</v>
       </c>
       <c r="F353" s="8">
-        <v>26.934799999999996</v>
+        <v>26.93</v>
       </c>
       <c r="G353" s="22">
         <v>490.00000000000006</v>
@@ -18567,7 +18567,7 @@
         <v>60</v>
       </c>
       <c r="F354" s="8">
-        <v>28.583500000000001</v>
+        <v>28.58</v>
       </c>
       <c r="G354" s="22">
         <v>210</v>
@@ -18590,7 +18590,7 @@
         <v>84</v>
       </c>
       <c r="F355" s="8">
-        <v>13.328600000000002</v>
+        <v>13.33</v>
       </c>
       <c r="G355" s="22">
         <v>630</v>
@@ -18613,7 +18613,7 @@
         <v>54</v>
       </c>
       <c r="F356" s="8">
-        <v>14.101900000000001</v>
+        <v>14.1</v>
       </c>
       <c r="G356" s="22">
         <v>383</v>
@@ -18636,7 +18636,7 @@
         <v>1116</v>
       </c>
       <c r="F357" s="8">
-        <v>193.60119999999989</v>
+        <v>193.6</v>
       </c>
       <c r="G357" s="22">
         <v>576</v>
@@ -18659,7 +18659,7 @@
         <v>528</v>
       </c>
       <c r="F358" s="8">
-        <v>359.06619999999992</v>
+        <v>359.07</v>
       </c>
       <c r="G358" s="22">
         <v>147</v>
@@ -18682,7 +18682,7 @@
         <v>1668</v>
       </c>
       <c r="F359" s="8">
-        <v>1005.4026999999992</v>
+        <v>1005.4</v>
       </c>
       <c r="G359" s="22">
         <v>166</v>
@@ -18705,7 +18705,7 @@
         <v>822</v>
       </c>
       <c r="F360" s="8">
-        <v>442.42840000000001</v>
+        <v>442.43</v>
       </c>
       <c r="G360" s="22">
         <v>186</v>
@@ -18728,7 +18728,7 @@
         <v>798</v>
       </c>
       <c r="F361" s="8">
-        <v>474.44770000000005</v>
+        <v>474.45</v>
       </c>
       <c r="G361" s="22">
         <v>168</v>
@@ -18751,7 +18751,7 @@
         <v>7428</v>
       </c>
       <c r="F362" s="8">
-        <v>4319.4956999999977</v>
+        <v>4319.5</v>
       </c>
       <c r="G362" s="22">
         <v>172</v>
@@ -18774,7 +18774,7 @@
         <v>324</v>
       </c>
       <c r="F363" s="8">
-        <v>172.23979999999997</v>
+        <v>172.24</v>
       </c>
       <c r="G363" s="22">
         <v>188</v>
@@ -18797,7 +18797,7 @@
         <v>2802</v>
       </c>
       <c r="F364" s="8">
-        <v>1515.4870999999998</v>
+        <v>1515.49</v>
       </c>
       <c r="G364" s="22">
         <v>185</v>
@@ -18820,7 +18820,7 @@
         <v>1914</v>
       </c>
       <c r="F365" s="8">
-        <v>1160.7160999999983</v>
+        <v>1160.72</v>
       </c>
       <c r="G365" s="22">
         <v>165</v>
@@ -18843,7 +18843,7 @@
         <v>2070</v>
       </c>
       <c r="F366" s="8">
-        <v>1192.8177999999994</v>
+        <v>1192.82</v>
       </c>
       <c r="G366" s="22">
         <v>174</v>
@@ -18866,7 +18866,7 @@
         <v>10068</v>
       </c>
       <c r="F367" s="8">
-        <v>5927.7117000000053</v>
+        <v>5927.71</v>
       </c>
       <c r="G367" s="22">
         <v>170</v>
@@ -18889,7 +18889,7 @@
         <v>444</v>
       </c>
       <c r="F368" s="8">
-        <v>431.32350000000014</v>
+        <v>431.32</v>
       </c>
       <c r="G368" s="22">
         <v>103</v>
@@ -18912,7 +18912,7 @@
         <v>1014</v>
       </c>
       <c r="F369" s="8">
-        <v>1012.727100000001</v>
+        <v>1012.73</v>
       </c>
       <c r="G369" s="22">
         <v>100</v>
@@ -18935,7 +18935,7 @@
         <v>1356</v>
       </c>
       <c r="F370" s="8">
-        <v>1489.2879000000009</v>
+        <v>1489.29</v>
       </c>
       <c r="G370" s="22">
         <v>91</v>
@@ -18958,7 +18958,7 @@
         <v>756</v>
       </c>
       <c r="F371" s="8">
-        <v>596.14339999999993</v>
+        <v>596.14</v>
       </c>
       <c r="G371" s="22">
         <v>127</v>
@@ -18981,7 +18981,7 @@
         <v>9558</v>
       </c>
       <c r="F372" s="8">
-        <v>10961.471799999988</v>
+        <v>10961.47</v>
       </c>
       <c r="G372" s="22">
         <v>87</v>
@@ -19004,7 +19004,7 @@
         <v>360</v>
       </c>
       <c r="F373" s="8">
-        <v>354.5822</v>
+        <v>354.58</v>
       </c>
       <c r="G373" s="22">
         <v>102</v>
@@ -19027,7 +19027,7 @@
         <v>3462</v>
       </c>
       <c r="F374" s="8">
-        <v>3375.9098000000008</v>
+        <v>3375.91</v>
       </c>
       <c r="G374" s="22">
         <v>103</v>
@@ -19050,7 +19050,7 @@
         <v>3168</v>
       </c>
       <c r="F375" s="8">
-        <v>3404.9569000000024</v>
+        <v>3404.96</v>
       </c>
       <c r="G375" s="22">
         <v>93</v>
@@ -19073,7 +19073,7 @@
         <v>1698</v>
       </c>
       <c r="F376" s="8">
-        <v>1762.7893000000001</v>
+        <v>1762.79</v>
       </c>
       <c r="G376" s="22">
         <v>96</v>
@@ -19096,7 +19096,7 @@
         <v>13614</v>
       </c>
       <c r="F377" s="8">
-        <v>14278.803899999986</v>
+        <v>14278.8</v>
       </c>
       <c r="G377" s="22">
         <v>95</v>
@@ -19119,7 +19119,7 @@
         <v>1740</v>
       </c>
       <c r="F378" s="8">
-        <v>6052.6203000000105</v>
+        <v>6052.62</v>
       </c>
       <c r="G378" s="22">
         <v>28.999999999999996</v>
@@ -19142,7 +19142,7 @@
         <v>5082</v>
       </c>
       <c r="F379" s="8">
-        <v>15615.115100000005</v>
+        <v>15615.12</v>
       </c>
       <c r="G379" s="22">
         <v>33</v>
@@ -19165,7 +19165,7 @@
         <v>5040</v>
       </c>
       <c r="F380" s="8">
-        <v>16965.22930000001</v>
+        <v>16965.23</v>
       </c>
       <c r="G380" s="22">
         <v>30</v>
@@ -19188,7 +19188,7 @@
         <v>2610</v>
       </c>
       <c r="F381" s="8">
-        <v>8484.7876000000142</v>
+        <v>8484.7900000000009</v>
       </c>
       <c r="G381" s="22">
         <v>31</v>
@@ -19211,7 +19211,7 @@
         <v>25860</v>
       </c>
       <c r="F382" s="8">
-        <v>90696.842600000004</v>
+        <v>90696.84</v>
       </c>
       <c r="G382" s="22">
         <v>28.999999999999996</v>
@@ -19234,7 +19234,7 @@
         <v>1272</v>
       </c>
       <c r="F383" s="8">
-        <v>4448.7469000000028</v>
+        <v>4448.75</v>
       </c>
       <c r="G383" s="22">
         <v>28.999999999999996</v>
@@ -19257,7 +19257,7 @@
         <v>9168</v>
       </c>
       <c r="F384" s="8">
-        <v>31646.479399999989</v>
+        <v>31646.48</v>
       </c>
       <c r="G384" s="22">
         <v>28.999999999999996</v>
@@ -19280,7 +19280,7 @@
         <v>6162</v>
       </c>
       <c r="F385" s="8">
-        <v>22715.57710000001</v>
+        <v>22715.58</v>
       </c>
       <c r="G385" s="22">
         <v>27</v>
@@ -19303,7 +19303,7 @@
         <v>9594</v>
       </c>
       <c r="F386" s="8">
-        <v>33781.149100000002</v>
+        <v>33781.15</v>
       </c>
       <c r="G386" s="22">
         <v>28.000000000000004</v>
@@ -19326,7 +19326,7 @@
         <v>42498</v>
       </c>
       <c r="F387" s="8">
-        <v>153589.77439999988</v>
+        <v>153589.76999999999</v>
       </c>
       <c r="G387" s="22">
         <v>28.000000000000004</v>
@@ -19349,7 +19349,7 @@
         <v>48</v>
       </c>
       <c r="F388" s="8">
-        <v>13.946600000000004</v>
+        <v>13.95</v>
       </c>
       <c r="G388" s="22">
         <v>344</v>
@@ -19372,7 +19372,7 @@
         <v>108</v>
       </c>
       <c r="F389" s="8">
-        <v>29.965800000000005</v>
+        <v>29.97</v>
       </c>
       <c r="G389" s="22">
         <v>360</v>
@@ -19395,7 +19395,7 @@
         <v>150</v>
       </c>
       <c r="F390" s="8">
-        <v>41.8705</v>
+        <v>41.87</v>
       </c>
       <c r="G390" s="22">
         <v>358</v>
@@ -19418,7 +19418,7 @@
         <v>84</v>
       </c>
       <c r="F391" s="8">
-        <v>18.563300000000002</v>
+        <v>18.559999999999999</v>
       </c>
       <c r="G391" s="22">
         <v>453</v>
@@ -19441,7 +19441,7 @@
         <v>588</v>
       </c>
       <c r="F392" s="8">
-        <v>115.56619999999998</v>
+        <v>115.57</v>
       </c>
       <c r="G392" s="22">
         <v>509</v>
@@ -19464,7 +19464,7 @@
         <v>84</v>
       </c>
       <c r="F393" s="8">
-        <v>13.974500000000001</v>
+        <v>13.97</v>
       </c>
       <c r="G393" s="22">
         <v>601</v>
@@ -19487,7 +19487,7 @@
         <v>126</v>
       </c>
       <c r="F394" s="8">
-        <v>60.2883</v>
+        <v>60.29</v>
       </c>
       <c r="G394" s="22">
         <v>209</v>
@@ -19510,7 +19510,7 @@
         <v>108</v>
       </c>
       <c r="F395" s="8">
-        <v>21.4815</v>
+        <v>21.48</v>
       </c>
       <c r="G395" s="22">
         <v>503</v>
@@ -19533,7 +19533,7 @@
         <v>102</v>
       </c>
       <c r="F396" s="8">
-        <v>32.693300000000001</v>
+        <v>32.69</v>
       </c>
       <c r="G396" s="22">
         <v>312</v>
@@ -19556,7 +19556,7 @@
         <v>1008</v>
       </c>
       <c r="F397" s="8">
-        <v>223.16759999999999</v>
+        <v>223.17</v>
       </c>
       <c r="G397" s="22">
         <v>451.99999999999994</v>
@@ -19579,7 +19579,7 @@
         <v>624</v>
       </c>
       <c r="F398" s="8">
-        <v>443.80980000000022</v>
+        <v>443.81</v>
       </c>
       <c r="G398" s="22">
         <v>141</v>
@@ -19602,7 +19602,7 @@
         <v>1968</v>
       </c>
       <c r="F399" s="8">
-        <v>1230.0017999999989</v>
+        <v>1230</v>
       </c>
       <c r="G399" s="22">
         <v>160</v>
@@ -19625,7 +19625,7 @@
         <v>948</v>
       </c>
       <c r="F400" s="8">
-        <v>580.79849999999988</v>
+        <v>580.79999999999995</v>
       </c>
       <c r="G400" s="22">
         <v>163</v>
@@ -19648,7 +19648,7 @@
         <v>1146</v>
       </c>
       <c r="F401" s="8">
-        <v>702.86720000000025</v>
+        <v>702.87</v>
       </c>
       <c r="G401" s="22">
         <v>163</v>
@@ -19671,7 +19671,7 @@
         <v>8172</v>
       </c>
       <c r="F402" s="8">
-        <v>4933.9702000000016</v>
+        <v>4933.97</v>
       </c>
       <c r="G402" s="22">
         <v>166</v>
@@ -19694,7 +19694,7 @@
         <v>696</v>
       </c>
       <c r="F403" s="8">
-        <v>410.28399999999982</v>
+        <v>410.28</v>
       </c>
       <c r="G403" s="22">
         <v>170</v>
@@ -19717,7 +19717,7 @@
         <v>3570</v>
       </c>
       <c r="F404" s="8">
-        <v>2091.8697000000006</v>
+        <v>2091.87</v>
       </c>
       <c r="G404" s="22">
         <v>171</v>
@@ -19740,7 +19740,7 @@
         <v>3756</v>
       </c>
       <c r="F405" s="8">
-        <v>2408.7380999999991</v>
+        <v>2408.7399999999998</v>
       </c>
       <c r="G405" s="22">
         <v>156</v>
@@ -19763,7 +19763,7 @@
         <v>13920</v>
       </c>
       <c r="F406" s="8">
-        <v>8531.7297000000035</v>
+        <v>8531.73</v>
       </c>
       <c r="G406" s="22">
         <v>163</v>
@@ -19786,7 +19786,7 @@
         <v>396</v>
       </c>
       <c r="F407" s="8">
-        <v>481.52839999999992</v>
+        <v>481.53</v>
       </c>
       <c r="G407" s="22">
         <v>82</v>
@@ -19809,7 +19809,7 @@
         <v>1176</v>
       </c>
       <c r="F408" s="8">
-        <v>1272.4762999999998</v>
+        <v>1272.48</v>
       </c>
       <c r="G408" s="22">
         <v>92</v>
@@ -19832,7 +19832,7 @@
         <v>1470</v>
       </c>
       <c r="F409" s="8">
-        <v>1544.8949000000009</v>
+        <v>1544.89</v>
       </c>
       <c r="G409" s="22">
         <v>95</v>
@@ -19855,7 +19855,7 @@
         <v>816</v>
       </c>
       <c r="F410" s="8">
-        <v>730.33880000000022</v>
+        <v>730.34</v>
       </c>
       <c r="G410" s="22">
         <v>112.00000000000001</v>
@@ -19878,7 +19878,7 @@
         <v>8742</v>
       </c>
       <c r="F411" s="8">
-        <v>10149.387600000007</v>
+        <v>10149.39</v>
       </c>
       <c r="G411" s="22">
         <v>86</v>
@@ -19901,7 +19901,7 @@
         <v>408</v>
       </c>
       <c r="F412" s="8">
-        <v>415.16499999999996</v>
+        <v>415.17</v>
       </c>
       <c r="G412" s="22">
         <v>98</v>
@@ -19924,7 +19924,7 @@
         <v>5964</v>
       </c>
       <c r="F413" s="8">
-        <v>7289.0863000000027</v>
+        <v>7289.09</v>
       </c>
       <c r="G413" s="22">
         <v>82</v>
@@ -19947,7 +19947,7 @@
         <v>3924</v>
       </c>
       <c r="F414" s="8">
-        <v>4633.4325000000017</v>
+        <v>4633.43</v>
       </c>
       <c r="G414" s="22">
         <v>85</v>
@@ -19970,7 +19970,7 @@
         <v>16884</v>
       </c>
       <c r="F415" s="8">
-        <v>19674.787000000004</v>
+        <v>19674.79</v>
       </c>
       <c r="G415" s="22">
         <v>86</v>
@@ -19993,7 +19993,7 @@
         <v>2610</v>
       </c>
       <c r="F416" s="8">
-        <v>9226.67580000001</v>
+        <v>9226.68</v>
       </c>
       <c r="G416" s="22">
         <v>28.000000000000004</v>
@@ -20016,7 +20016,7 @@
         <v>6480</v>
       </c>
       <c r="F417" s="8">
-        <v>22154.447800000031</v>
+        <v>22154.45</v>
       </c>
       <c r="G417" s="22">
         <v>28.999999999999996</v>
@@ -20039,7 +20039,7 @@
         <v>5598</v>
       </c>
       <c r="F418" s="8">
-        <v>18738.228400000022</v>
+        <v>18738.23</v>
       </c>
       <c r="G418" s="22">
         <v>30</v>
@@ -20062,7 +20062,7 @@
         <v>3444</v>
       </c>
       <c r="F419" s="8">
-        <v>12437.795800000014</v>
+        <v>12437.8</v>
       </c>
       <c r="G419" s="22">
         <v>28.000000000000004</v>
@@ -20085,7 +20085,7 @@
         <v>27084</v>
       </c>
       <c r="F420" s="8">
-        <v>95745.993200000084</v>
+        <v>95745.99</v>
       </c>
       <c r="G420" s="22">
         <v>28.000000000000004</v>
@@ -20108,7 +20108,7 @@
         <v>1944</v>
       </c>
       <c r="F421" s="8">
-        <v>6898.9210999999968</v>
+        <v>6898.92</v>
       </c>
       <c r="G421" s="22">
         <v>28.000000000000004</v>
@@ -20131,7 +20131,7 @@
         <v>8412</v>
       </c>
       <c r="F422" s="8">
-        <v>27829.896300000019</v>
+        <v>27829.9</v>
       </c>
       <c r="G422" s="22">
         <v>30</v>
@@ -20154,7 +20154,7 @@
         <v>8958</v>
       </c>
       <c r="F423" s="8">
-        <v>33111.519800000038</v>
+        <v>33111.519999999997</v>
       </c>
       <c r="G423" s="22">
         <v>27</v>
@@ -20177,7 +20177,7 @@
         <v>48672</v>
       </c>
       <c r="F424" s="8">
-        <v>173399.85649999982</v>
+        <v>173399.86</v>
       </c>
       <c r="G424" s="22">
         <v>28.000000000000004</v>
@@ -20200,7 +20200,7 @@
         <v>48</v>
       </c>
       <c r="F425" s="8">
-        <v>25.374599999999997</v>
+        <v>25.37</v>
       </c>
       <c r="G425" s="22">
         <v>189</v>
@@ -20223,7 +20223,7 @@
         <v>162</v>
       </c>
       <c r="F426" s="8">
-        <v>41.622900000000001</v>
+        <v>41.62</v>
       </c>
       <c r="G426" s="22">
         <v>389</v>
@@ -20246,7 +20246,7 @@
         <v>114</v>
       </c>
       <c r="F427" s="8">
-        <v>29.898899999999998</v>
+        <v>29.9</v>
       </c>
       <c r="G427" s="22">
         <v>381</v>
@@ -20269,7 +20269,7 @@
         <v>126</v>
       </c>
       <c r="F428" s="8">
-        <v>31.0749</v>
+        <v>31.07</v>
       </c>
       <c r="G428" s="22">
         <v>405</v>
@@ -20292,7 +20292,7 @@
         <v>732</v>
       </c>
       <c r="F429" s="8">
-        <v>158.76060000000001</v>
+        <v>158.76</v>
       </c>
       <c r="G429" s="22">
         <v>461.00000000000006</v>
@@ -20315,7 +20315,7 @@
         <v>132</v>
       </c>
       <c r="F430" s="8">
-        <v>33.943799999999996</v>
+        <v>33.94</v>
       </c>
       <c r="G430" s="22">
         <v>389</v>
@@ -20338,7 +20338,7 @@
         <v>114</v>
       </c>
       <c r="F431" s="8">
-        <v>42.346499999999999</v>
+        <v>42.35</v>
       </c>
       <c r="G431" s="22">
         <v>269</v>
@@ -20361,7 +20361,7 @@
         <v>330</v>
       </c>
       <c r="F432" s="8">
-        <v>81.25269999999999</v>
+        <v>81.25</v>
       </c>
       <c r="G432" s="22">
         <v>405.99999999999994</v>
@@ -20384,7 +20384,7 @@
         <v>1860</v>
       </c>
       <c r="F433" s="8">
-        <v>407.97959999999983</v>
+        <v>407.98</v>
       </c>
       <c r="G433" s="22">
         <v>455.99999999999994</v>
@@ -20407,7 +20407,7 @@
         <v>468</v>
       </c>
       <c r="F434" s="8">
-        <v>355.36159999999978</v>
+        <v>355.36</v>
       </c>
       <c r="G434" s="22">
         <v>132</v>
@@ -20430,7 +20430,7 @@
         <v>1920</v>
       </c>
       <c r="F435" s="8">
-        <v>1246.2288000000005</v>
+        <v>1246.23</v>
       </c>
       <c r="G435" s="22">
         <v>154</v>
@@ -20453,7 +20453,7 @@
         <v>1194</v>
       </c>
       <c r="F436" s="8">
-        <v>746.01600000000008</v>
+        <v>746.02</v>
       </c>
       <c r="G436" s="22">
         <v>160</v>
@@ -20476,7 +20476,7 @@
         <v>1278</v>
       </c>
       <c r="F437" s="8">
-        <v>784.35999999999979</v>
+        <v>784.36</v>
       </c>
       <c r="G437" s="22">
         <v>163</v>
@@ -20499,7 +20499,7 @@
         <v>9336</v>
       </c>
       <c r="F438" s="8">
-        <v>5903.0576000000037</v>
+        <v>5903.06</v>
       </c>
       <c r="G438" s="22">
         <v>158</v>
@@ -20522,7 +20522,7 @@
         <v>1362</v>
       </c>
       <c r="F439" s="8">
-        <v>1027.5555999999999</v>
+        <v>1027.56</v>
       </c>
       <c r="G439" s="22">
         <v>133</v>
@@ -20545,7 +20545,7 @@
         <v>3888</v>
       </c>
       <c r="F440" s="8">
-        <v>2362.3136000000027</v>
+        <v>2362.31</v>
       </c>
       <c r="G440" s="22">
         <v>165</v>
@@ -20568,7 +20568,7 @@
         <v>5550</v>
       </c>
       <c r="F441" s="8">
-        <v>3865.9908000000046</v>
+        <v>3865.99</v>
       </c>
       <c r="G441" s="22">
         <v>144</v>
@@ -20591,7 +20591,7 @@
         <v>3408</v>
       </c>
       <c r="F442" s="8">
-        <v>2093.9136000000017</v>
+        <v>2093.91</v>
       </c>
       <c r="G442" s="22">
         <v>163</v>
@@ -20614,7 +20614,7 @@
         <v>16824</v>
       </c>
       <c r="F443" s="8">
-        <v>10640.828000000001</v>
+        <v>10640.83</v>
       </c>
       <c r="G443" s="22">
         <v>158</v>
@@ -20637,7 +20637,7 @@
         <v>258</v>
       </c>
       <c r="F444" s="8">
-        <v>311.95339999999999</v>
+        <v>311.95</v>
       </c>
       <c r="G444" s="22">
         <v>83</v>
@@ -20660,7 +20660,7 @@
         <v>558</v>
       </c>
       <c r="F445" s="8">
-        <v>627.77629999999988</v>
+        <v>627.78</v>
       </c>
       <c r="G445" s="22">
         <v>89</v>
@@ -20683,7 +20683,7 @@
         <v>750</v>
       </c>
       <c r="F446" s="8">
-        <v>720.51150000000052</v>
+        <v>720.51</v>
       </c>
       <c r="G446" s="22">
         <v>104</v>
@@ -20706,7 +20706,7 @@
         <v>540</v>
       </c>
       <c r="F447" s="8">
-        <v>536.40010000000007</v>
+        <v>536.4</v>
       </c>
       <c r="G447" s="22">
         <v>101</v>
@@ -20729,7 +20729,7 @@
         <v>5202</v>
       </c>
       <c r="F448" s="8">
-        <v>6266.6671000000015</v>
+        <v>6266.67</v>
       </c>
       <c r="G448" s="22">
         <v>83</v>
@@ -20752,7 +20752,7 @@
         <v>336</v>
       </c>
       <c r="F449" s="8">
-        <v>298.87390000000005</v>
+        <v>298.87</v>
       </c>
       <c r="G449" s="22">
         <v>112.00000000000001</v>
@@ -20775,7 +20775,7 @@
         <v>2622</v>
       </c>
       <c r="F450" s="8">
-        <v>3047.900799999999</v>
+        <v>3047.9</v>
       </c>
       <c r="G450" s="22">
         <v>86</v>
@@ -20798,7 +20798,7 @@
         <v>2640</v>
       </c>
       <c r="F451" s="8">
-        <v>3193.5704000000023</v>
+        <v>3193.57</v>
       </c>
       <c r="G451" s="22">
         <v>83</v>
@@ -20821,7 +20821,7 @@
         <v>1398</v>
       </c>
       <c r="F452" s="8">
-        <v>1761.3045000000013</v>
+        <v>1761.3</v>
       </c>
       <c r="G452" s="22">
         <v>79</v>
@@ -20844,7 +20844,7 @@
         <v>13938</v>
       </c>
       <c r="F453" s="8">
-        <v>17443.393100000005</v>
+        <v>17443.39</v>
       </c>
       <c r="G453" s="22">
         <v>80</v>
@@ -20867,7 +20867,7 @@
         <v>2934</v>
       </c>
       <c r="F454" s="8">
-        <v>10314.601600000011</v>
+        <v>10314.6</v>
       </c>
       <c r="G454" s="22">
         <v>28.000000000000004</v>
@@ -20890,7 +20890,7 @@
         <v>7104</v>
       </c>
       <c r="F455" s="8">
-        <v>24768.840700000012</v>
+        <v>24768.84</v>
       </c>
       <c r="G455" s="22">
         <v>28.999999999999996</v>
@@ -20913,7 +20913,7 @@
         <v>5406</v>
       </c>
       <c r="F456" s="8">
-        <v>18734.994200000008</v>
+        <v>18734.990000000002</v>
       </c>
       <c r="G456" s="22">
         <v>28.999999999999996</v>
@@ -20936,7 +20936,7 @@
         <v>3708</v>
       </c>
       <c r="F457" s="8">
-        <v>13529.632600000003</v>
+        <v>13529.63</v>
       </c>
       <c r="G457" s="22">
         <v>27</v>
@@ -20959,7 +20959,7 @@
         <v>25080</v>
       </c>
       <c r="F458" s="8">
-        <v>90819.619300000253</v>
+        <v>90819.62</v>
       </c>
       <c r="G458" s="22">
         <v>28.000000000000004</v>
@@ -20982,7 +20982,7 @@
         <v>2922</v>
       </c>
       <c r="F459" s="8">
-        <v>8483.0512000000053</v>
+        <v>8483.0499999999993</v>
       </c>
       <c r="G459" s="22">
         <v>34</v>
@@ -21005,7 +21005,7 @@
         <v>10164</v>
       </c>
       <c r="F460" s="8">
-        <v>36355.357200000028</v>
+        <v>36355.360000000001</v>
       </c>
       <c r="G460" s="22">
         <v>28.000000000000004</v>
@@ -21028,7 +21028,7 @@
         <v>10404</v>
       </c>
       <c r="F461" s="8">
-        <v>39704.687200000073</v>
+        <v>39704.69</v>
       </c>
       <c r="G461" s="22">
         <v>26</v>
@@ -21051,7 +21051,7 @@
         <v>13104</v>
       </c>
       <c r="F462" s="8">
-        <v>47706.265100000033</v>
+        <v>47706.27</v>
       </c>
       <c r="G462" s="22">
         <v>27</v>
@@ -21074,7 +21074,7 @@
         <v>56610</v>
       </c>
       <c r="F463" s="8">
-        <v>211437.62749999959</v>
+        <v>211437.63</v>
       </c>
       <c r="G463" s="22">
         <v>27</v>
@@ -21097,7 +21097,7 @@
         <v>30</v>
       </c>
       <c r="F464" s="8">
-        <v>7.8519999999999994</v>
+        <v>7.85</v>
       </c>
       <c r="G464" s="22">
         <v>382</v>
@@ -21120,7 +21120,7 @@
         <v>96</v>
       </c>
       <c r="F465" s="8">
-        <v>38.2166</v>
+        <v>38.22</v>
       </c>
       <c r="G465" s="22">
         <v>250.99999999999997</v>
@@ -21143,7 +21143,7 @@
         <v>192</v>
       </c>
       <c r="F466" s="8">
-        <v>50.219799999999992</v>
+        <v>50.22</v>
       </c>
       <c r="G466" s="22">
         <v>382</v>
@@ -21166,7 +21166,7 @@
         <v>96</v>
       </c>
       <c r="F467" s="8">
-        <v>31.151000000000003</v>
+        <v>31.15</v>
       </c>
       <c r="G467" s="22">
         <v>308</v>
@@ -21189,7 +21189,7 @@
         <v>510</v>
       </c>
       <c r="F468" s="8">
-        <v>131.75809999999998</v>
+        <v>131.76</v>
       </c>
       <c r="G468" s="22">
         <v>387</v>
@@ -21212,7 +21212,7 @@
         <v>30</v>
       </c>
       <c r="F469" s="8">
-        <v>8.4093999999999998</v>
+        <v>8.41</v>
       </c>
       <c r="G469" s="22">
         <v>357</v>
@@ -21235,7 +21235,7 @@
         <v>102</v>
       </c>
       <c r="F470" s="8">
-        <v>37.016199999999998</v>
+        <v>37.020000000000003</v>
       </c>
       <c r="G470" s="22">
         <v>276</v>
@@ -21258,7 +21258,7 @@
         <v>108</v>
       </c>
       <c r="F471" s="8">
-        <v>33.881999999999998</v>
+        <v>33.880000000000003</v>
       </c>
       <c r="G471" s="22">
         <v>319</v>
@@ -21281,7 +21281,7 @@
         <v>126</v>
       </c>
       <c r="F472" s="8">
-        <v>32.494799999999998</v>
+        <v>32.49</v>
       </c>
       <c r="G472" s="22">
         <v>388</v>
@@ -21304,7 +21304,7 @@
         <v>1638</v>
       </c>
       <c r="F473" s="13">
-        <v>347.0877000000001</v>
+        <v>347.09</v>
       </c>
       <c r="G473" s="23">
         <v>472</v>
@@ -21327,7 +21327,7 @@
         <v>1158</v>
       </c>
       <c r="F474" s="5">
-        <v>732.19460000000038</v>
+        <v>732.19</v>
       </c>
       <c r="G474" s="21">
         <v>158</v>
@@ -21350,7 +21350,7 @@
         <v>966</v>
       </c>
       <c r="F475" s="8">
-        <v>466.47439999999989</v>
+        <v>466.47</v>
       </c>
       <c r="G475" s="22">
         <v>206.99999999999997</v>
@@ -21373,7 +21373,7 @@
         <v>684</v>
       </c>
       <c r="F476" s="8">
-        <v>382.07399999999978</v>
+        <v>382.07</v>
       </c>
       <c r="G476" s="22">
         <v>179</v>
@@ -21396,7 +21396,7 @@
         <v>594</v>
       </c>
       <c r="F477" s="8">
-        <v>342.14619999999991</v>
+        <v>342.15</v>
       </c>
       <c r="G477" s="22">
         <v>174</v>
@@ -21419,7 +21419,7 @@
         <v>1962</v>
       </c>
       <c r="F478" s="8">
-        <v>1100.9928</v>
+        <v>1100.99</v>
       </c>
       <c r="G478" s="22">
         <v>178</v>
@@ -21442,7 +21442,7 @@
         <v>186</v>
       </c>
       <c r="F479" s="8">
-        <v>95.317300000000031</v>
+        <v>95.32</v>
       </c>
       <c r="G479" s="22">
         <v>195</v>
@@ -21465,7 +21465,7 @@
         <v>2820</v>
       </c>
       <c r="F480" s="8">
-        <v>1398.5200000000009</v>
+        <v>1398.52</v>
       </c>
       <c r="G480" s="22">
         <v>202</v>
@@ -21488,7 +21488,7 @@
         <v>1656</v>
       </c>
       <c r="F481" s="8">
-        <v>902.54160000000047</v>
+        <v>902.54</v>
       </c>
       <c r="G481" s="22">
         <v>183</v>
@@ -21511,7 +21511,7 @@
         <v>558</v>
       </c>
       <c r="F482" s="8">
-        <v>295.05160000000001</v>
+        <v>295.05</v>
       </c>
       <c r="G482" s="22">
         <v>189</v>
@@ -21534,7 +21534,7 @@
         <v>1788</v>
       </c>
       <c r="F483" s="8">
-        <v>1007.9515000000002</v>
+        <v>1007.95</v>
       </c>
       <c r="G483" s="22">
         <v>177</v>
@@ -21557,7 +21557,7 @@
         <v>930</v>
       </c>
       <c r="F484" s="8">
-        <v>908.29650000000095</v>
+        <v>908.3</v>
       </c>
       <c r="G484" s="22">
         <v>102</v>
@@ -21580,7 +21580,7 @@
         <v>1830</v>
       </c>
       <c r="F485" s="8">
-        <v>1687.2192000000002</v>
+        <v>1687.22</v>
       </c>
       <c r="G485" s="22">
         <v>108</v>
@@ -21603,7 +21603,7 @@
         <v>1878</v>
       </c>
       <c r="F486" s="8">
-        <v>1689.7806000000007</v>
+        <v>1689.78</v>
       </c>
       <c r="G486" s="22">
         <v>111.00000000000001</v>
@@ -21626,7 +21626,7 @@
         <v>1092</v>
       </c>
       <c r="F487" s="8">
-        <v>925.66700000000083</v>
+        <v>925.67</v>
       </c>
       <c r="G487" s="22">
         <v>118</v>
@@ -21649,7 +21649,7 @@
         <v>5934</v>
       </c>
       <c r="F488" s="8">
-        <v>6074.4284999999863</v>
+        <v>6074.43</v>
       </c>
       <c r="G488" s="22">
         <v>98</v>
@@ -21672,7 +21672,7 @@
         <v>240</v>
       </c>
       <c r="F489" s="8">
-        <v>198.8869</v>
+        <v>198.89</v>
       </c>
       <c r="G489" s="22">
         <v>121</v>
@@ -21695,7 +21695,7 @@
         <v>5340</v>
       </c>
       <c r="F490" s="8">
-        <v>4325.9334999999974</v>
+        <v>4325.93</v>
       </c>
       <c r="G490" s="22">
         <v>123</v>
@@ -21718,7 +21718,7 @@
         <v>3156</v>
       </c>
       <c r="F491" s="8">
-        <v>3148.5878000000007</v>
+        <v>3148.59</v>
       </c>
       <c r="G491" s="22">
         <v>100</v>
@@ -21741,7 +21741,7 @@
         <v>1170</v>
       </c>
       <c r="F492" s="8">
-        <v>1061.428900000001</v>
+        <v>1061.43</v>
       </c>
       <c r="G492" s="22">
         <v>110.00000000000001</v>
@@ -21764,7 +21764,7 @@
         <v>3762</v>
       </c>
       <c r="F493" s="8">
-        <v>3580.7050000000017</v>
+        <v>3580.71</v>
       </c>
       <c r="G493" s="22">
         <v>105</v>
@@ -21787,7 +21787,7 @@
         <v>2382</v>
       </c>
       <c r="F494" s="8">
-        <v>7925.6679999999969</v>
+        <v>7925.67</v>
       </c>
       <c r="G494" s="22">
         <v>30</v>
@@ -21810,7 +21810,7 @@
         <v>3516</v>
       </c>
       <c r="F495" s="8">
-        <v>11526.183199999992</v>
+        <v>11526.18</v>
       </c>
       <c r="G495" s="22">
         <v>31</v>
@@ -21833,7 +21833,7 @@
         <v>3156</v>
       </c>
       <c r="F496" s="8">
-        <v>10703.470499999987</v>
+        <v>10703.47</v>
       </c>
       <c r="G496" s="22">
         <v>28.999999999999996</v>
@@ -21856,7 +21856,7 @@
         <v>2316</v>
       </c>
       <c r="F497" s="8">
-        <v>7852.3945999999951</v>
+        <v>7852.39</v>
       </c>
       <c r="G497" s="22">
         <v>28.999999999999996</v>
@@ -21879,7 +21879,7 @@
         <v>7254</v>
       </c>
       <c r="F498" s="8">
-        <v>24031.802099999979</v>
+        <v>24031.8</v>
       </c>
       <c r="G498" s="22">
         <v>30</v>
@@ -21902,7 +21902,7 @@
         <v>666</v>
       </c>
       <c r="F499" s="8">
-        <v>2216.5640999999991</v>
+        <v>2216.56</v>
       </c>
       <c r="G499" s="22">
         <v>30</v>
@@ -21925,7 +21925,7 @@
         <v>8772</v>
       </c>
       <c r="F500" s="8">
-        <v>29896.282299999973</v>
+        <v>29896.28</v>
       </c>
       <c r="G500" s="22">
         <v>28.999999999999996</v>
@@ -21948,7 +21948,7 @@
         <v>4992</v>
       </c>
       <c r="F501" s="8">
-        <v>17051.432300000004</v>
+        <v>17051.43</v>
       </c>
       <c r="G501" s="22">
         <v>28.999999999999996</v>
@@ -21971,7 +21971,7 @@
         <v>3306</v>
       </c>
       <c r="F502" s="8">
-        <v>11624.311099999995</v>
+        <v>11624.31</v>
       </c>
       <c r="G502" s="22">
         <v>28.000000000000004</v>
@@ -21994,7 +21994,7 @@
         <v>9672</v>
       </c>
       <c r="F503" s="8">
-        <v>34684.726999999984</v>
+        <v>34684.730000000003</v>
       </c>
       <c r="G503" s="22">
         <v>28.000000000000004</v>
@@ -22017,7 +22017,7 @@
         <v>66</v>
       </c>
       <c r="F504" s="8">
-        <v>15.971799999999996</v>
+        <v>15.97</v>
       </c>
       <c r="G504" s="22">
         <v>413</v>
@@ -22040,7 +22040,7 @@
         <v>102</v>
       </c>
       <c r="F505" s="8">
-        <v>17.851399999999998</v>
+        <v>17.850000000000001</v>
       </c>
       <c r="G505" s="22">
         <v>571</v>
@@ -22063,7 +22063,7 @@
         <v>30</v>
       </c>
       <c r="F506" s="8">
-        <v>12.9224</v>
+        <v>12.92</v>
       </c>
       <c r="G506" s="22">
         <v>231.99999999999997</v>
@@ -22086,7 +22086,7 @@
         <v>60</v>
       </c>
       <c r="F507" s="8">
-        <v>13.790599999999998</v>
+        <v>13.79</v>
       </c>
       <c r="G507" s="22">
         <v>434.99999999999994</v>
@@ -22109,7 +22109,7 @@
         <v>114</v>
       </c>
       <c r="F508" s="8">
-        <v>44.393000000000001</v>
+        <v>44.39</v>
       </c>
       <c r="G508" s="22">
         <v>257</v>
@@ -22132,7 +22132,7 @@
         <v>42</v>
       </c>
       <c r="F509" s="8">
-        <v>18.220600000000001</v>
+        <v>18.22</v>
       </c>
       <c r="G509" s="22">
         <v>231</v>
@@ -22155,7 +22155,7 @@
         <v>84</v>
       </c>
       <c r="F510" s="8">
-        <v>39.443599999999996</v>
+        <v>39.44</v>
       </c>
       <c r="G510" s="22">
         <v>213</v>
@@ -22178,7 +22178,7 @@
         <v>210</v>
       </c>
       <c r="F511" s="8">
-        <v>63.483400000000024</v>
+        <v>63.48</v>
       </c>
       <c r="G511" s="22">
         <v>331</v>
@@ -22201,7 +22201,7 @@
         <v>36</v>
       </c>
       <c r="F512" s="8">
-        <v>17.680800000000001</v>
+        <v>17.68</v>
       </c>
       <c r="G512" s="22">
         <v>204</v>
@@ -22224,7 +22224,7 @@
         <v>264</v>
       </c>
       <c r="F513" s="8">
-        <v>116.54540000000001</v>
+        <v>116.55</v>
       </c>
       <c r="G513" s="22">
         <v>227</v>
@@ -22247,7 +22247,7 @@
         <v>2028</v>
       </c>
       <c r="F514" s="8">
-        <v>1406.2745000000025</v>
+        <v>1406.27</v>
       </c>
       <c r="G514" s="22">
         <v>144</v>
@@ -22270,7 +22270,7 @@
         <v>1728</v>
       </c>
       <c r="F515" s="8">
-        <v>950.28199999999924</v>
+        <v>950.28</v>
       </c>
       <c r="G515" s="22">
         <v>182</v>
@@ -22293,7 +22293,7 @@
         <v>1032</v>
       </c>
       <c r="F516" s="8">
-        <v>585.08979999999951</v>
+        <v>585.09</v>
       </c>
       <c r="G516" s="22">
         <v>176</v>
@@ -22316,7 +22316,7 @@
         <v>792</v>
       </c>
       <c r="F517" s="8">
-        <v>457.4430000000001</v>
+        <v>457.44</v>
       </c>
       <c r="G517" s="22">
         <v>173</v>
@@ -22339,7 +22339,7 @@
         <v>2952</v>
       </c>
       <c r="F518" s="8">
-        <v>1717.1438000000012</v>
+        <v>1717.14</v>
       </c>
       <c r="G518" s="22">
         <v>172</v>
@@ -22362,7 +22362,7 @@
         <v>312</v>
       </c>
       <c r="F519" s="8">
-        <v>163.95969999999994</v>
+        <v>163.96</v>
       </c>
       <c r="G519" s="22">
         <v>190</v>
@@ -22385,7 +22385,7 @@
         <v>4152</v>
       </c>
       <c r="F520" s="8">
-        <v>2222.8803000000012</v>
+        <v>2222.88</v>
       </c>
       <c r="G520" s="22">
         <v>187</v>
@@ -22408,7 +22408,7 @@
         <v>3000</v>
       </c>
       <c r="F521" s="8">
-        <v>1787.7698</v>
+        <v>1787.77</v>
       </c>
       <c r="G521" s="22">
         <v>168</v>
@@ -22431,7 +22431,7 @@
         <v>1056</v>
       </c>
       <c r="F522" s="8">
-        <v>565.44849999999997</v>
+        <v>565.45000000000005</v>
       </c>
       <c r="G522" s="22">
         <v>187</v>
@@ -22454,7 +22454,7 @@
         <v>3090</v>
       </c>
       <c r="F523" s="8">
-        <v>1806.5610000000006</v>
+        <v>1806.56</v>
       </c>
       <c r="G523" s="22">
         <v>171</v>
@@ -22477,7 +22477,7 @@
         <v>1374</v>
       </c>
       <c r="F524" s="8">
-        <v>1398.6225000000006</v>
+        <v>1398.62</v>
       </c>
       <c r="G524" s="22">
         <v>98</v>
@@ -22500,7 +22500,7 @@
         <v>2892</v>
       </c>
       <c r="F525" s="8">
-        <v>2679.3567999999968</v>
+        <v>2679.36</v>
       </c>
       <c r="G525" s="22">
         <v>108</v>
@@ -22523,7 +22523,7 @@
         <v>2718</v>
       </c>
       <c r="F526" s="8">
-        <v>2531.005599999999</v>
+        <v>2531.0100000000002</v>
       </c>
       <c r="G526" s="22">
         <v>107</v>
@@ -22546,7 +22546,7 @@
         <v>1452</v>
       </c>
       <c r="F527" s="8">
-        <v>1306.8188000000002</v>
+        <v>1306.82</v>
       </c>
       <c r="G527" s="22">
         <v>111.00000000000001</v>
@@ -22569,7 +22569,7 @@
         <v>7608</v>
       </c>
       <c r="F528" s="8">
-        <v>7868.7598999999864</v>
+        <v>7868.76</v>
       </c>
       <c r="G528" s="22">
         <v>97</v>
@@ -22592,7 +22592,7 @@
         <v>450</v>
       </c>
       <c r="F529" s="8">
-        <v>482.65110000000016</v>
+        <v>482.65</v>
       </c>
       <c r="G529" s="22">
         <v>93</v>
@@ -22615,7 +22615,7 @@
         <v>9114</v>
       </c>
       <c r="F530" s="8">
-        <v>8170.6495999999943</v>
+        <v>8170.65</v>
       </c>
       <c r="G530" s="22">
         <v>112.00000000000001</v>
@@ -22638,7 +22638,7 @@
         <v>7230</v>
       </c>
       <c r="F531" s="8">
-        <v>7589.8322999999864</v>
+        <v>7589.83</v>
       </c>
       <c r="G531" s="22">
         <v>95</v>
@@ -22661,7 +22661,7 @@
         <v>2208</v>
       </c>
       <c r="F532" s="8">
-        <v>1987.1340000000018</v>
+        <v>1987.13</v>
       </c>
       <c r="G532" s="22">
         <v>111.00000000000001</v>
@@ -22684,7 +22684,7 @@
         <v>5604</v>
       </c>
       <c r="F533" s="8">
-        <v>5627.9654999999984</v>
+        <v>5627.97</v>
       </c>
       <c r="G533" s="22">
         <v>100</v>
@@ -22707,7 +22707,7 @@
         <v>10008</v>
       </c>
       <c r="F534" s="8">
-        <v>34600.402499999909</v>
+        <v>34600.400000000001</v>
       </c>
       <c r="G534" s="22">
         <v>28.999999999999996</v>
@@ -22730,7 +22730,7 @@
         <v>10698</v>
       </c>
       <c r="F535" s="8">
-        <v>33215.715499999984</v>
+        <v>33215.72</v>
       </c>
       <c r="G535" s="22">
         <v>32</v>
@@ -22753,7 +22753,7 @@
         <v>10068</v>
       </c>
       <c r="F536" s="8">
-        <v>33166.197800000009</v>
+        <v>33166.199999999997</v>
       </c>
       <c r="G536" s="22">
         <v>30</v>
@@ -22776,7 +22776,7 @@
         <v>4428</v>
       </c>
       <c r="F537" s="8">
-        <v>14539.175400000016</v>
+        <v>14539.18</v>
       </c>
       <c r="G537" s="22">
         <v>30</v>
@@ -22799,7 +22799,7 @@
         <v>16086</v>
       </c>
       <c r="F538" s="8">
-        <v>51493.011299999955</v>
+        <v>51493.01</v>
       </c>
       <c r="G538" s="22">
         <v>31</v>
@@ -22822,7 +22822,7 @@
         <v>1734</v>
       </c>
       <c r="F539" s="8">
-        <v>5476.9013999999997</v>
+        <v>5476.9</v>
       </c>
       <c r="G539" s="22">
         <v>32</v>
@@ -22845,7 +22845,7 @@
         <v>23184</v>
       </c>
       <c r="F540" s="8">
-        <v>76312.446400000059</v>
+        <v>76312.45</v>
       </c>
       <c r="G540" s="22">
         <v>30</v>
@@ -22868,7 +22868,7 @@
         <v>13824</v>
       </c>
       <c r="F541" s="8">
-        <v>47730.768199999904</v>
+        <v>47730.77</v>
       </c>
       <c r="G541" s="22">
         <v>28.999999999999996</v>
@@ -22891,7 +22891,7 @@
         <v>7620</v>
       </c>
       <c r="F542" s="8">
-        <v>23970.906899999991</v>
+        <v>23970.91</v>
       </c>
       <c r="G542" s="22">
         <v>32</v>
@@ -22914,7 +22914,7 @@
         <v>18912</v>
       </c>
       <c r="F543" s="8">
-        <v>64478.128499999977</v>
+        <v>64478.13</v>
       </c>
       <c r="G543" s="22">
         <v>28.999999999999996</v>
@@ -22937,7 +22937,7 @@
         <v>192</v>
       </c>
       <c r="F544" s="8">
-        <v>41.488700000000001</v>
+        <v>41.49</v>
       </c>
       <c r="G544" s="22">
         <v>463</v>
@@ -22960,7 +22960,7 @@
         <v>384</v>
       </c>
       <c r="F545" s="8">
-        <v>92.147800000000018</v>
+        <v>92.15</v>
       </c>
       <c r="G545" s="22">
         <v>417</v>
@@ -22983,7 +22983,7 @@
         <v>108</v>
       </c>
       <c r="F546" s="8">
-        <v>29.680099999999996</v>
+        <v>29.68</v>
       </c>
       <c r="G546" s="22">
         <v>364</v>
@@ -23006,7 +23006,7 @@
         <v>180</v>
       </c>
       <c r="F547" s="8">
-        <v>27.341100000000001</v>
+        <v>27.34</v>
       </c>
       <c r="G547" s="22">
         <v>658</v>
@@ -23029,7 +23029,7 @@
         <v>312</v>
       </c>
       <c r="F548" s="8">
-        <v>99.100500000000039</v>
+        <v>99.1</v>
       </c>
       <c r="G548" s="22">
         <v>315</v>
@@ -23052,7 +23052,7 @@
         <v>102</v>
       </c>
       <c r="F549" s="8">
-        <v>24.908200000000001</v>
+        <v>24.91</v>
       </c>
       <c r="G549" s="22">
         <v>409.99999999999994</v>
@@ -23075,7 +23075,7 @@
         <v>336</v>
       </c>
       <c r="F550" s="8">
-        <v>95.691700000000012</v>
+        <v>95.69</v>
       </c>
       <c r="G550" s="22">
         <v>351</v>
@@ -23098,7 +23098,7 @@
         <v>486</v>
       </c>
       <c r="F551" s="8">
-        <v>126.08610000000004</v>
+        <v>126.09</v>
       </c>
       <c r="G551" s="22">
         <v>385</v>
@@ -23121,7 +23121,7 @@
         <v>84</v>
       </c>
       <c r="F552" s="8">
-        <v>34.968999999999994</v>
+        <v>34.97</v>
       </c>
       <c r="G552" s="22">
         <v>240</v>
@@ -23144,7 +23144,7 @@
         <v>504</v>
       </c>
       <c r="F553" s="8">
-        <v>104.94410000000005</v>
+        <v>104.94</v>
       </c>
       <c r="G553" s="22">
         <v>480</v>
@@ -23167,7 +23167,7 @@
         <v>1470</v>
       </c>
       <c r="F554" s="8">
-        <v>1007.1779999999998</v>
+        <v>1007.18</v>
       </c>
       <c r="G554" s="22">
         <v>146</v>
@@ -23190,7 +23190,7 @@
         <v>1386</v>
       </c>
       <c r="F555" s="8">
-        <v>747.63839999999982</v>
+        <v>747.64</v>
       </c>
       <c r="G555" s="22">
         <v>185</v>
@@ -23213,7 +23213,7 @@
         <v>828</v>
       </c>
       <c r="F556" s="8">
-        <v>461.97629999999992</v>
+        <v>461.98</v>
       </c>
       <c r="G556" s="22">
         <v>179</v>
@@ -23236,7 +23236,7 @@
         <v>786</v>
       </c>
       <c r="F557" s="8">
-        <v>439.33739999999989</v>
+        <v>439.34</v>
       </c>
       <c r="G557" s="22">
         <v>179</v>
@@ -23259,7 +23259,7 @@
         <v>2136</v>
       </c>
       <c r="F558" s="8">
-        <v>1331.8226999999974</v>
+        <v>1331.82</v>
       </c>
       <c r="G558" s="22">
         <v>160</v>
@@ -23282,7 +23282,7 @@
         <v>258</v>
       </c>
       <c r="F559" s="8">
-        <v>123.8549</v>
+        <v>123.85</v>
       </c>
       <c r="G559" s="22">
         <v>208</v>
@@ -23305,7 +23305,7 @@
         <v>2790</v>
       </c>
       <c r="F560" s="8">
-        <v>1514.5492999999988</v>
+        <v>1514.55</v>
       </c>
       <c r="G560" s="22">
         <v>184</v>
@@ -23328,7 +23328,7 @@
         <v>1890</v>
       </c>
       <c r="F561" s="8">
-        <v>1069.1119999999994</v>
+        <v>1069.1099999999999</v>
       </c>
       <c r="G561" s="22">
         <v>177</v>
@@ -23351,7 +23351,7 @@
         <v>996</v>
       </c>
       <c r="F562" s="8">
-        <v>541.21429999999987</v>
+        <v>541.21</v>
       </c>
       <c r="G562" s="22">
         <v>184</v>
@@ -23374,7 +23374,7 @@
         <v>3444</v>
       </c>
       <c r="F563" s="8">
-        <v>2147.7852999999973</v>
+        <v>2147.79</v>
       </c>
       <c r="G563" s="22">
         <v>160</v>
@@ -23397,7 +23397,7 @@
         <v>846</v>
       </c>
       <c r="F564" s="8">
-        <v>890.30309999999861</v>
+        <v>890.3</v>
       </c>
       <c r="G564" s="22">
         <v>95</v>
@@ -23420,7 +23420,7 @@
         <v>1554</v>
       </c>
       <c r="F565" s="8">
-        <v>1726.575900000001</v>
+        <v>1726.58</v>
       </c>
       <c r="G565" s="22">
         <v>90</v>
@@ -23443,7 +23443,7 @@
         <v>684</v>
       </c>
       <c r="F566" s="8">
-        <v>655.3611999999996</v>
+        <v>655.36</v>
       </c>
       <c r="G566" s="22">
         <v>104</v>
@@ -23466,7 +23466,7 @@
         <v>762</v>
       </c>
       <c r="F567" s="8">
-        <v>767.62909999999977</v>
+        <v>767.63</v>
       </c>
       <c r="G567" s="22">
         <v>99</v>
@@ -23489,7 +23489,7 @@
         <v>4296</v>
       </c>
       <c r="F568" s="8">
-        <v>4941.821800000007</v>
+        <v>4941.82</v>
       </c>
       <c r="G568" s="22">
         <v>87</v>
@@ -23512,7 +23512,7 @@
         <v>264</v>
       </c>
       <c r="F569" s="8">
-        <v>282.02030000000002</v>
+        <v>282.02</v>
       </c>
       <c r="G569" s="22">
         <v>94</v>
@@ -23535,7 +23535,7 @@
         <v>2694</v>
       </c>
       <c r="F570" s="8">
-        <v>2533.9861999999985</v>
+        <v>2533.9899999999998</v>
       </c>
       <c r="G570" s="22">
         <v>106</v>
@@ -23558,7 +23558,7 @@
         <v>2040</v>
       </c>
       <c r="F571" s="8">
-        <v>2257.801100000002</v>
+        <v>2257.8000000000002</v>
       </c>
       <c r="G571" s="22">
         <v>90</v>
@@ -23581,7 +23581,7 @@
         <v>1620</v>
       </c>
       <c r="F572" s="8">
-        <v>1728.3381000000004</v>
+        <v>1728.34</v>
       </c>
       <c r="G572" s="22">
         <v>94</v>
@@ -23604,7 +23604,7 @@
         <v>4134</v>
       </c>
       <c r="F573" s="8">
-        <v>4318.4670000000042</v>
+        <v>4318.47</v>
       </c>
       <c r="G573" s="22">
         <v>96</v>
@@ -23627,7 +23627,7 @@
         <v>8604</v>
       </c>
       <c r="F574" s="8">
-        <v>29023.345000000001</v>
+        <v>29023.35</v>
       </c>
       <c r="G574" s="22">
         <v>30</v>
@@ -23650,7 +23650,7 @@
         <v>11010</v>
       </c>
       <c r="F575" s="8">
-        <v>34254.105300000025</v>
+        <v>34254.11</v>
       </c>
       <c r="G575" s="22">
         <v>32</v>
@@ -23673,7 +23673,7 @@
         <v>6792</v>
       </c>
       <c r="F576" s="8">
-        <v>23856.36729999998</v>
+        <v>23856.37</v>
       </c>
       <c r="G576" s="22">
         <v>28.000000000000004</v>
@@ -23696,7 +23696,7 @@
         <v>3618</v>
       </c>
       <c r="F577" s="8">
-        <v>12257.8856</v>
+        <v>12257.89</v>
       </c>
       <c r="G577" s="22">
         <v>30</v>
@@ -23719,7 +23719,7 @@
         <v>14298</v>
       </c>
       <c r="F578" s="8">
-        <v>45616.654200000012</v>
+        <v>45616.65</v>
       </c>
       <c r="G578" s="22">
         <v>31</v>
@@ -23742,7 +23742,7 @@
         <v>1548</v>
       </c>
       <c r="F579" s="8">
-        <v>5148.0335999999979</v>
+        <v>5148.03</v>
       </c>
       <c r="G579" s="22">
         <v>30</v>
@@ -23765,7 +23765,7 @@
         <v>12630</v>
       </c>
       <c r="F580" s="8">
-        <v>41297.919100000021</v>
+        <v>41297.919999999998</v>
       </c>
       <c r="G580" s="22">
         <v>31</v>
@@ -23788,7 +23788,7 @@
         <v>7518</v>
       </c>
       <c r="F581" s="8">
-        <v>25430.02169999999</v>
+        <v>25430.02</v>
       </c>
       <c r="G581" s="22">
         <v>30</v>
@@ -23811,7 +23811,7 @@
         <v>6828</v>
       </c>
       <c r="F582" s="8">
-        <v>23105.246199999987</v>
+        <v>23105.25</v>
       </c>
       <c r="G582" s="22">
         <v>30</v>
@@ -23834,7 +23834,7 @@
         <v>17754</v>
       </c>
       <c r="F583" s="8">
-        <v>62424.26249999999</v>
+        <v>62424.26</v>
       </c>
       <c r="G583" s="22">
         <v>28.000000000000004</v>
@@ -23857,7 +23857,7 @@
         <v>66</v>
       </c>
       <c r="F584" s="8">
-        <v>14.694400000000002</v>
+        <v>14.69</v>
       </c>
       <c r="G584" s="22">
         <v>449</v>
@@ -23880,7 +23880,7 @@
         <v>252</v>
       </c>
       <c r="F585" s="8">
-        <v>57.425599999999989</v>
+        <v>57.43</v>
       </c>
       <c r="G585" s="22">
         <v>438.99999999999994</v>
@@ -23903,7 +23903,7 @@
         <v>90</v>
       </c>
       <c r="F586" s="8">
-        <v>14.4696</v>
+        <v>14.47</v>
       </c>
       <c r="G586" s="22">
         <v>622</v>
@@ -23926,7 +23926,7 @@
         <v>114</v>
       </c>
       <c r="F587" s="8">
-        <v>21.543299999999999</v>
+        <v>21.54</v>
       </c>
       <c r="G587" s="22">
         <v>529</v>
@@ -23949,7 +23949,7 @@
         <v>324</v>
       </c>
       <c r="F588" s="8">
-        <v>79.862000000000023</v>
+        <v>79.86</v>
       </c>
       <c r="G588" s="22">
         <v>405.99999999999994</v>
@@ -23972,7 +23972,7 @@
         <v>120</v>
       </c>
       <c r="F589" s="8">
-        <v>29.1508</v>
+        <v>29.15</v>
       </c>
       <c r="G589" s="22">
         <v>412</v>
@@ -23995,7 +23995,7 @@
         <v>84</v>
       </c>
       <c r="F590" s="8">
-        <v>22.419999999999998</v>
+        <v>22.42</v>
       </c>
       <c r="G590" s="22">
         <v>375</v>
@@ -24018,7 +24018,7 @@
         <v>216</v>
       </c>
       <c r="F591" s="8">
-        <v>58.867499999999978</v>
+        <v>58.87</v>
       </c>
       <c r="G591" s="22">
         <v>367</v>
@@ -24041,7 +24041,7 @@
         <v>102</v>
       </c>
       <c r="F592" s="8">
-        <v>28.061399999999995</v>
+        <v>28.06</v>
       </c>
       <c r="G592" s="22">
         <v>363</v>
@@ -24064,7 +24064,7 @@
         <v>636</v>
       </c>
       <c r="F593" s="8">
-        <v>138.01660000000004</v>
+        <v>138.02000000000001</v>
       </c>
       <c r="G593" s="22">
         <v>461.00000000000006</v>
@@ -24087,7 +24087,7 @@
         <v>1776</v>
       </c>
       <c r="F594" s="8">
-        <v>1254.6547999999991</v>
+        <v>1254.6500000000001</v>
       </c>
       <c r="G594" s="22">
         <v>142</v>
@@ -24110,7 +24110,7 @@
         <v>1920</v>
       </c>
       <c r="F595" s="8">
-        <v>1111.8628999999994</v>
+        <v>1111.8599999999999</v>
       </c>
       <c r="G595" s="22">
         <v>173</v>
@@ -24133,7 +24133,7 @@
         <v>1242</v>
       </c>
       <c r="F596" s="8">
-        <v>707.57309999999995</v>
+        <v>707.57</v>
       </c>
       <c r="G596" s="22">
         <v>176</v>
@@ -24156,7 +24156,7 @@
         <v>1068</v>
       </c>
       <c r="F597" s="8">
-        <v>626.60909999999956</v>
+        <v>626.61</v>
       </c>
       <c r="G597" s="22">
         <v>170</v>
@@ -24179,7 +24179,7 @@
         <v>3294</v>
       </c>
       <c r="F598" s="8">
-        <v>1938.5637000000004</v>
+        <v>1938.56</v>
       </c>
       <c r="G598" s="22">
         <v>170</v>
@@ -24202,7 +24202,7 @@
         <v>396</v>
       </c>
       <c r="F599" s="8">
-        <v>232.24909999999988</v>
+        <v>232.25</v>
       </c>
       <c r="G599" s="22">
         <v>171</v>
@@ -24225,7 +24225,7 @@
         <v>5208</v>
       </c>
       <c r="F600" s="8">
-        <v>2854.2860999999984</v>
+        <v>2854.29</v>
       </c>
       <c r="G600" s="22">
         <v>182</v>
@@ -24248,7 +24248,7 @@
         <v>2682</v>
       </c>
       <c r="F601" s="8">
-        <v>1623.7938000000017</v>
+        <v>1623.79</v>
       </c>
       <c r="G601" s="22">
         <v>165</v>
@@ -24271,7 +24271,7 @@
         <v>1638</v>
       </c>
       <c r="F602" s="8">
-        <v>943.92699999999957</v>
+        <v>943.93</v>
       </c>
       <c r="G602" s="22">
         <v>174</v>
@@ -24294,7 +24294,7 @@
         <v>4926</v>
       </c>
       <c r="F603" s="8">
-        <v>2987.1681999999978</v>
+        <v>2987.17</v>
       </c>
       <c r="G603" s="22">
         <v>165</v>
@@ -24317,7 +24317,7 @@
         <v>1398</v>
       </c>
       <c r="F604" s="8">
-        <v>1624.2673999999993</v>
+        <v>1624.27</v>
       </c>
       <c r="G604" s="22">
         <v>86</v>
@@ -24340,7 +24340,7 @@
         <v>2166</v>
       </c>
       <c r="F605" s="8">
-        <v>2127.2073</v>
+        <v>2127.21</v>
       </c>
       <c r="G605" s="22">
         <v>102</v>
@@ -24363,7 +24363,7 @@
         <v>1656</v>
       </c>
       <c r="F606" s="8">
-        <v>1565.0908000000002</v>
+        <v>1565.09</v>
       </c>
       <c r="G606" s="22">
         <v>106</v>
@@ -24386,7 +24386,7 @@
         <v>1296</v>
       </c>
       <c r="F607" s="8">
-        <v>1353.6673000000003</v>
+        <v>1353.67</v>
       </c>
       <c r="G607" s="22">
         <v>96</v>
@@ -24409,7 +24409,7 @@
         <v>5274</v>
       </c>
       <c r="F608" s="8">
-        <v>5854.3673999999901</v>
+        <v>5854.37</v>
       </c>
       <c r="G608" s="22">
         <v>90</v>
@@ -24432,7 +24432,7 @@
         <v>366</v>
       </c>
       <c r="F609" s="8">
-        <v>378.28809999999993</v>
+        <v>378.29</v>
       </c>
       <c r="G609" s="22">
         <v>97</v>
@@ -24455,7 +24455,7 @@
         <v>6960</v>
       </c>
       <c r="F610" s="8">
-        <v>6997.9237999999841</v>
+        <v>6997.92</v>
       </c>
       <c r="G610" s="22">
         <v>99</v>
@@ -24478,7 +24478,7 @@
         <v>4374</v>
       </c>
       <c r="F611" s="8">
-        <v>4667.8862000000054</v>
+        <v>4667.8900000000003</v>
       </c>
       <c r="G611" s="22">
         <v>94</v>
@@ -24501,7 +24501,7 @@
         <v>1992</v>
       </c>
       <c r="F612" s="8">
-        <v>2035.1365000000005</v>
+        <v>2035.14</v>
       </c>
       <c r="G612" s="22">
         <v>98</v>
@@ -24524,7 +24524,7 @@
         <v>7026</v>
       </c>
       <c r="F613" s="8">
-        <v>7336.7944999999945</v>
+        <v>7336.79</v>
       </c>
       <c r="G613" s="22">
         <v>96</v>
@@ -24547,7 +24547,7 @@
         <v>5652</v>
       </c>
       <c r="F614" s="8">
-        <v>19048.077599999957</v>
+        <v>19048.080000000002</v>
       </c>
       <c r="G614" s="22">
         <v>30</v>
@@ -24570,7 +24570,7 @@
         <v>8730</v>
       </c>
       <c r="F615" s="8">
-        <v>27067.305199999984</v>
+        <v>27067.31</v>
       </c>
       <c r="G615" s="22">
         <v>32</v>
@@ -24593,7 +24593,7 @@
         <v>6942</v>
       </c>
       <c r="F616" s="8">
-        <v>23261.210999999978</v>
+        <v>23261.21</v>
       </c>
       <c r="G616" s="22">
         <v>30</v>
@@ -24616,7 +24616,7 @@
         <v>4464</v>
       </c>
       <c r="F617" s="8">
-        <v>14682.498200000011</v>
+        <v>14682.5</v>
       </c>
       <c r="G617" s="22">
         <v>30</v>
@@ -24639,7 +24639,7 @@
         <v>13734</v>
       </c>
       <c r="F618" s="8">
-        <v>45671.048000000003</v>
+        <v>45671.05</v>
       </c>
       <c r="G618" s="22">
         <v>30</v>
@@ -24662,7 +24662,7 @@
         <v>1896</v>
       </c>
       <c r="F619" s="8">
-        <v>6470.3444</v>
+        <v>6470.34</v>
       </c>
       <c r="G619" s="22">
         <v>28.999999999999996</v>
@@ -24685,7 +24685,7 @@
         <v>16848</v>
       </c>
       <c r="F620" s="8">
-        <v>53669.541499999912</v>
+        <v>53669.54</v>
       </c>
       <c r="G620" s="22">
         <v>31</v>
@@ -24708,7 +24708,7 @@
         <v>8766</v>
       </c>
       <c r="F621" s="8">
-        <v>31362.530499999964</v>
+        <v>31362.53</v>
       </c>
       <c r="G621" s="22">
         <v>28.000000000000004</v>
@@ -24731,7 +24731,7 @@
         <v>7608</v>
       </c>
       <c r="F622" s="8">
-        <v>25290.464999999997</v>
+        <v>25290.47</v>
       </c>
       <c r="G622" s="22">
         <v>30</v>
@@ -24754,7 +24754,7 @@
         <v>22512</v>
       </c>
       <c r="F623" s="8">
-        <v>80390.078499999989</v>
+        <v>80390.080000000002</v>
       </c>
       <c r="G623" s="22">
         <v>28.000000000000004</v>
@@ -24777,7 +24777,7 @@
         <v>114</v>
       </c>
       <c r="F624" s="8">
-        <v>20.774999999999999</v>
+        <v>20.78</v>
       </c>
       <c r="G624" s="22">
         <v>549</v>
@@ -24800,7 +24800,7 @@
         <v>228</v>
       </c>
       <c r="F625" s="8">
-        <v>47.738000000000014</v>
+        <v>47.74</v>
       </c>
       <c r="G625" s="22">
         <v>478</v>
@@ -24823,7 +24823,7 @@
         <v>120</v>
       </c>
       <c r="F626" s="8">
-        <v>35.014800000000001</v>
+        <v>35.01</v>
       </c>
       <c r="G626" s="22">
         <v>343</v>
@@ -24846,7 +24846,7 @@
         <v>78</v>
       </c>
       <c r="F627" s="8">
-        <v>17.013000000000005</v>
+        <v>17.010000000000002</v>
       </c>
       <c r="G627" s="22">
         <v>458</v>
@@ -24869,7 +24869,7 @@
         <v>318</v>
       </c>
       <c r="F628" s="8">
-        <v>70.7346</v>
+        <v>70.73</v>
       </c>
       <c r="G628" s="22">
         <v>450</v>
@@ -24892,7 +24892,7 @@
         <v>120</v>
       </c>
       <c r="F629" s="8">
-        <v>28.509599999999999</v>
+        <v>28.51</v>
       </c>
       <c r="G629" s="22">
         <v>421</v>
@@ -24915,7 +24915,7 @@
         <v>144</v>
       </c>
       <c r="F630" s="8">
-        <v>72.590400000000017</v>
+        <v>72.59</v>
       </c>
       <c r="G630" s="22">
         <v>198</v>
@@ -24938,7 +24938,7 @@
         <v>168</v>
       </c>
       <c r="F631" s="8">
-        <v>40.559200000000011</v>
+        <v>40.56</v>
       </c>
       <c r="G631" s="22">
         <v>413.99999999999994</v>
@@ -24961,7 +24961,7 @@
         <v>102</v>
       </c>
       <c r="F632" s="8">
-        <v>39.697000000000017</v>
+        <v>39.700000000000003</v>
       </c>
       <c r="G632" s="22">
         <v>257</v>
@@ -24984,7 +24984,7 @@
         <v>480</v>
       </c>
       <c r="F633" s="8">
-        <v>99.077999999999989</v>
+        <v>99.08</v>
       </c>
       <c r="G633" s="22">
         <v>484</v>
@@ -25007,7 +25007,7 @@
         <v>2736</v>
       </c>
       <c r="F634" s="8">
-        <v>1996.9053000000001</v>
+        <v>1996.91</v>
       </c>
       <c r="G634" s="22">
         <v>137</v>
@@ -25030,7 +25030,7 @@
         <v>2220</v>
       </c>
       <c r="F635" s="8">
-        <v>1311.1168999999993</v>
+        <v>1311.12</v>
       </c>
       <c r="G635" s="22">
         <v>169</v>
@@ -25053,7 +25053,7 @@
         <v>1350</v>
       </c>
       <c r="F636" s="8">
-        <v>798.24289999999837</v>
+        <v>798.24</v>
       </c>
       <c r="G636" s="22">
         <v>169</v>
@@ -25076,7 +25076,7 @@
         <v>1260</v>
       </c>
       <c r="F637" s="8">
-        <v>749.32329999999934</v>
+        <v>749.32</v>
       </c>
       <c r="G637" s="22">
         <v>168</v>
@@ -25099,7 +25099,7 @@
         <v>3522</v>
       </c>
       <c r="F638" s="8">
-        <v>2037.8937999999985</v>
+        <v>2037.89</v>
       </c>
       <c r="G638" s="22">
         <v>173</v>
@@ -25122,7 +25122,7 @@
         <v>504</v>
       </c>
       <c r="F639" s="8">
-        <v>303.51909999999998</v>
+        <v>303.52</v>
       </c>
       <c r="G639" s="22">
         <v>166</v>
@@ -25145,7 +25145,7 @@
         <v>7110</v>
       </c>
       <c r="F640" s="8">
-        <v>4265.2068000000036</v>
+        <v>4265.21</v>
       </c>
       <c r="G640" s="22">
         <v>167</v>
@@ -25168,7 +25168,7 @@
         <v>5256</v>
       </c>
       <c r="F641" s="8">
-        <v>3327.052800000004</v>
+        <v>3327.05</v>
       </c>
       <c r="G641" s="22">
         <v>158</v>
@@ -25191,7 +25191,7 @@
         <v>6516</v>
       </c>
       <c r="F642" s="8">
-        <v>3988.0434000000014</v>
+        <v>3988.04</v>
       </c>
       <c r="G642" s="22">
         <v>163</v>
@@ -25214,7 +25214,7 @@
         <v>1494</v>
       </c>
       <c r="F643" s="8">
-        <v>1750.8383000000006</v>
+        <v>1750.84</v>
       </c>
       <c r="G643" s="22">
         <v>85</v>
@@ -25237,7 +25237,7 @@
         <v>2310</v>
       </c>
       <c r="F644" s="8">
-        <v>2297.1803000000004</v>
+        <v>2297.1799999999998</v>
       </c>
       <c r="G644" s="22">
         <v>101</v>
@@ -25260,7 +25260,7 @@
         <v>2088</v>
       </c>
       <c r="F645" s="8">
-        <v>2143.9263999999989</v>
+        <v>2143.9299999999998</v>
       </c>
       <c r="G645" s="22">
         <v>97</v>
@@ -25283,7 +25283,7 @@
         <v>1260</v>
       </c>
       <c r="F646" s="8">
-        <v>1385.3041999999994</v>
+        <v>1385.3</v>
       </c>
       <c r="G646" s="22">
         <v>91</v>
@@ -25306,7 +25306,7 @@
         <v>4488</v>
       </c>
       <c r="F647" s="8">
-        <v>5210.1625000000031</v>
+        <v>5210.16</v>
       </c>
       <c r="G647" s="22">
         <v>86</v>
@@ -25329,7 +25329,7 @@
         <v>420</v>
       </c>
       <c r="F648" s="8">
-        <v>454.80169999999987</v>
+        <v>454.8</v>
       </c>
       <c r="G648" s="22">
         <v>92</v>
@@ -25352,7 +25352,7 @@
         <v>9792</v>
       </c>
       <c r="F649" s="8">
-        <v>10824.814</v>
+        <v>10824.81</v>
       </c>
       <c r="G649" s="22">
         <v>90</v>
@@ -25375,7 +25375,7 @@
         <v>5958</v>
       </c>
       <c r="F650" s="8">
-        <v>7148.3273999999892</v>
+        <v>7148.33</v>
       </c>
       <c r="G650" s="22">
         <v>83</v>
@@ -25398,7 +25398,7 @@
         <v>7698</v>
       </c>
       <c r="F651" s="8">
-        <v>8794.2083999999959</v>
+        <v>8794.2099999999991</v>
       </c>
       <c r="G651" s="22">
         <v>88</v>
@@ -25421,7 +25421,7 @@
         <v>6942</v>
       </c>
       <c r="F652" s="8">
-        <v>23708.250499999809</v>
+        <v>23708.25</v>
       </c>
       <c r="G652" s="22">
         <v>28.999999999999996</v>
@@ -25444,7 +25444,7 @@
         <v>11040</v>
       </c>
       <c r="F653" s="8">
-        <v>35832.41949999996</v>
+        <v>35832.42</v>
       </c>
       <c r="G653" s="22">
         <v>31</v>
@@ -25467,7 +25467,7 @@
         <v>7974</v>
       </c>
       <c r="F654" s="8">
-        <v>27985.865099999934</v>
+        <v>27985.87</v>
       </c>
       <c r="G654" s="22">
         <v>28.000000000000004</v>
@@ -25490,7 +25490,7 @@
         <v>4212</v>
       </c>
       <c r="F655" s="8">
-        <v>14832.57080000004</v>
+        <v>14832.57</v>
       </c>
       <c r="G655" s="22">
         <v>28.000000000000004</v>
@@ -25513,7 +25513,7 @@
         <v>13110</v>
       </c>
       <c r="F656" s="8">
-        <v>45740.105699999869</v>
+        <v>45740.11</v>
       </c>
       <c r="G656" s="22">
         <v>28.999999999999996</v>
@@ -25536,7 +25536,7 @@
         <v>2124</v>
       </c>
       <c r="F657" s="8">
-        <v>7650.1847000000043</v>
+        <v>7650.18</v>
       </c>
       <c r="G657" s="22">
         <v>28.000000000000004</v>
@@ -25559,7 +25559,7 @@
         <v>18312</v>
       </c>
       <c r="F658" s="8">
-        <v>60160.207399999905</v>
+        <v>60160.21</v>
       </c>
       <c r="G658" s="22">
         <v>30</v>
@@ -25582,7 +25582,7 @@
         <v>12156</v>
       </c>
       <c r="F659" s="8">
-        <v>43611.211699999862</v>
+        <v>43611.21</v>
       </c>
       <c r="G659" s="22">
         <v>28.000000000000004</v>
@@ -25605,7 +25605,7 @@
         <v>25218</v>
       </c>
       <c r="F660" s="8">
-        <v>92220.720700000034</v>
+        <v>92220.72</v>
       </c>
       <c r="G660" s="22">
         <v>27</v>
@@ -25628,7 +25628,7 @@
         <v>156</v>
       </c>
       <c r="F661" s="8">
-        <v>53.262600000000006</v>
+        <v>53.26</v>
       </c>
       <c r="G661" s="22">
         <v>293</v>
@@ -25651,7 +25651,7 @@
         <v>252</v>
       </c>
       <c r="F662" s="8">
-        <v>55.802200000000006</v>
+        <v>55.8</v>
       </c>
       <c r="G662" s="22">
         <v>451.99999999999994</v>
@@ -25674,7 +25674,7 @@
         <v>126</v>
       </c>
       <c r="F663" s="8">
-        <v>50.615500000000004</v>
+        <v>50.62</v>
       </c>
       <c r="G663" s="22">
         <v>249.00000000000003</v>
@@ -25697,7 +25697,7 @@
         <v>96</v>
       </c>
       <c r="F664" s="8">
-        <v>23.077100000000005</v>
+        <v>23.08</v>
       </c>
       <c r="G664" s="22">
         <v>416</v>
@@ -25720,7 +25720,7 @@
         <v>402</v>
       </c>
       <c r="F665" s="8">
-        <v>106.21600000000002</v>
+        <v>106.22</v>
       </c>
       <c r="G665" s="22">
         <v>378</v>
@@ -25743,7 +25743,7 @@
         <v>60</v>
       </c>
       <c r="F666" s="8">
-        <v>17.240200000000002</v>
+        <v>17.239999999999998</v>
       </c>
       <c r="G666" s="22">
         <v>348</v>
@@ -25766,7 +25766,7 @@
         <v>210</v>
       </c>
       <c r="F667" s="8">
-        <v>74.184700000000007</v>
+        <v>74.180000000000007</v>
       </c>
       <c r="G667" s="22">
         <v>283</v>
@@ -25789,7 +25789,7 @@
         <v>300</v>
       </c>
       <c r="F668" s="8">
-        <v>84.248800000000003</v>
+        <v>84.25</v>
       </c>
       <c r="G668" s="22">
         <v>356</v>
@@ -25812,7 +25812,7 @@
         <v>858</v>
       </c>
       <c r="F669" s="8">
-        <v>204.16310000000004</v>
+        <v>204.16</v>
       </c>
       <c r="G669" s="22">
         <v>420</v>
@@ -25835,7 +25835,7 @@
         <v>2568</v>
       </c>
       <c r="F670" s="8">
-        <v>1869.2482999999993</v>
+        <v>1869.25</v>
       </c>
       <c r="G670" s="22">
         <v>137</v>
@@ -25858,7 +25858,7 @@
         <v>2010</v>
       </c>
       <c r="F671" s="8">
-        <v>1218.6139999999998</v>
+        <v>1218.6099999999999</v>
       </c>
       <c r="G671" s="22">
         <v>165</v>
@@ -25881,7 +25881,7 @@
         <v>1452</v>
       </c>
       <c r="F672" s="8">
-        <v>875.51300000000049</v>
+        <v>875.51</v>
       </c>
       <c r="G672" s="22">
         <v>166</v>
@@ -25904,7 +25904,7 @@
         <v>1260</v>
       </c>
       <c r="F673" s="8">
-        <v>774.55200000000025</v>
+        <v>774.55</v>
       </c>
       <c r="G673" s="22">
         <v>163</v>
@@ -25927,7 +25927,7 @@
         <v>3948</v>
       </c>
       <c r="F674" s="8">
-        <v>2344.8543000000009</v>
+        <v>2344.85</v>
       </c>
       <c r="G674" s="22">
         <v>168</v>
@@ -25950,7 +25950,7 @@
         <v>960</v>
       </c>
       <c r="F675" s="8">
-        <v>686.1585</v>
+        <v>686.16</v>
       </c>
       <c r="G675" s="22">
         <v>140</v>
@@ -25973,7 +25973,7 @@
         <v>8556</v>
       </c>
       <c r="F676" s="8">
-        <v>5205.2008999999998</v>
+        <v>5205.2</v>
       </c>
       <c r="G676" s="22">
         <v>164</v>
@@ -25996,7 +25996,7 @@
         <v>7740</v>
       </c>
       <c r="F677" s="8">
-        <v>5212.3706999999977</v>
+        <v>5212.37</v>
       </c>
       <c r="G677" s="22">
         <v>148</v>
@@ -26019,7 +26019,7 @@
         <v>2598</v>
       </c>
       <c r="F678" s="8">
-        <v>1554.5725999999997</v>
+        <v>1554.57</v>
       </c>
       <c r="G678" s="22">
         <v>167</v>
@@ -26042,7 +26042,7 @@
         <v>7386</v>
       </c>
       <c r="F679" s="8">
-        <v>4738.4909999999991</v>
+        <v>4738.49</v>
       </c>
       <c r="G679" s="22">
         <v>156</v>
@@ -26065,7 +26065,7 @@
         <v>1116</v>
       </c>
       <c r="F680" s="8">
-        <v>1335.3570999999988</v>
+        <v>1335.36</v>
       </c>
       <c r="G680" s="22">
         <v>84</v>
@@ -26088,7 +26088,7 @@
         <v>1056</v>
       </c>
       <c r="F681" s="8">
-        <v>1184.902</v>
+        <v>1184.9000000000001</v>
       </c>
       <c r="G681" s="22">
         <v>89</v>
@@ -26111,7 +26111,7 @@
         <v>996</v>
       </c>
       <c r="F682" s="8">
-        <v>972.60130000000038</v>
+        <v>972.6</v>
       </c>
       <c r="G682" s="22">
         <v>102</v>
@@ -26134,7 +26134,7 @@
         <v>1008</v>
       </c>
       <c r="F683" s="8">
-        <v>1008.8171000000003</v>
+        <v>1008.82</v>
       </c>
       <c r="G683" s="22">
         <v>100</v>
@@ -26157,7 +26157,7 @@
         <v>2532</v>
       </c>
       <c r="F684" s="8">
-        <v>2883.1875999999993</v>
+        <v>2883.19</v>
       </c>
       <c r="G684" s="22">
         <v>88</v>
@@ -26180,7 +26180,7 @@
         <v>426</v>
       </c>
       <c r="F685" s="8">
-        <v>452.21460000000025</v>
+        <v>452.21</v>
       </c>
       <c r="G685" s="22">
         <v>94</v>
@@ -26203,7 +26203,7 @@
         <v>5226</v>
       </c>
       <c r="F686" s="8">
-        <v>5913.849199999996</v>
+        <v>5913.85</v>
       </c>
       <c r="G686" s="22">
         <v>88</v>
@@ -26226,7 +26226,7 @@
         <v>3858</v>
       </c>
       <c r="F687" s="8">
-        <v>4403.5692999999947</v>
+        <v>4403.57</v>
       </c>
       <c r="G687" s="22">
         <v>88</v>
@@ -26249,7 +26249,7 @@
         <v>1194</v>
       </c>
       <c r="F688" s="8">
-        <v>1436.9529999999995</v>
+        <v>1436.95</v>
       </c>
       <c r="G688" s="22">
         <v>83</v>
@@ -26272,7 +26272,7 @@
         <v>7386</v>
       </c>
       <c r="F689" s="8">
-        <v>9010.0182999999925</v>
+        <v>9010.02</v>
       </c>
       <c r="G689" s="22">
         <v>82</v>
@@ -26295,7 +26295,7 @@
         <v>7128</v>
       </c>
       <c r="F690" s="8">
-        <v>24286.604600000126</v>
+        <v>24286.6</v>
       </c>
       <c r="G690" s="22">
         <v>28.999999999999996</v>
@@ -26318,7 +26318,7 @@
         <v>10260</v>
       </c>
       <c r="F691" s="8">
-        <v>32393.822500000038</v>
+        <v>32393.82</v>
       </c>
       <c r="G691" s="22">
         <v>32</v>
@@ -26341,7 +26341,7 @@
         <v>7950</v>
       </c>
       <c r="F692" s="8">
-        <v>27576.709700000018</v>
+        <v>27576.71</v>
       </c>
       <c r="G692" s="22">
         <v>28.999999999999996</v>
@@ -26364,7 +26364,7 @@
         <v>4998</v>
       </c>
       <c r="F693" s="8">
-        <v>17360.019999999993</v>
+        <v>17360.02</v>
       </c>
       <c r="G693" s="22">
         <v>28.999999999999996</v>
@@ -26387,7 +26387,7 @@
         <v>12402</v>
       </c>
       <c r="F694" s="8">
-        <v>43223.1826</v>
+        <v>43223.18</v>
       </c>
       <c r="G694" s="22">
         <v>28.999999999999996</v>
@@ -26410,7 +26410,7 @@
         <v>2490</v>
       </c>
       <c r="F695" s="8">
-        <v>7651.7341999999899</v>
+        <v>7651.73</v>
       </c>
       <c r="G695" s="22">
         <v>33</v>
@@ -26433,7 +26433,7 @@
         <v>23328</v>
       </c>
       <c r="F696" s="8">
-        <v>82679.964999999982</v>
+        <v>82679.97</v>
       </c>
       <c r="G696" s="22">
         <v>28.000000000000004</v>
@@ -26456,7 +26456,7 @@
         <v>15936</v>
       </c>
       <c r="F697" s="8">
-        <v>59393.79540000001</v>
+        <v>59393.8</v>
       </c>
       <c r="G697" s="22">
         <v>27</v>
@@ -26479,7 +26479,7 @@
         <v>9918</v>
       </c>
       <c r="F698" s="8">
-        <v>34830.997500000019</v>
+        <v>34831</v>
       </c>
       <c r="G698" s="22">
         <v>28.000000000000004</v>
@@ -26502,7 +26502,7 @@
         <v>29454</v>
       </c>
       <c r="F699" s="8">
-        <v>110887.18029999975</v>
+        <v>110887.18</v>
       </c>
       <c r="G699" s="22">
         <v>27</v>
@@ -26525,7 +26525,7 @@
         <v>174</v>
       </c>
       <c r="F700" s="8">
-        <v>61.658699999999996</v>
+        <v>61.66</v>
       </c>
       <c r="G700" s="22">
         <v>282</v>
@@ -26548,7 +26548,7 @@
         <v>258</v>
       </c>
       <c r="F701" s="8">
-        <v>62.391799999999996</v>
+        <v>62.39</v>
       </c>
       <c r="G701" s="22">
         <v>413.99999999999994</v>
@@ -26571,7 +26571,7 @@
         <v>120</v>
       </c>
       <c r="F702" s="8">
-        <v>60.383400000000002</v>
+        <v>60.38</v>
       </c>
       <c r="G702" s="22">
         <v>199</v>
@@ -26594,7 +26594,7 @@
         <v>102</v>
       </c>
       <c r="F703" s="8">
-        <v>26.008400000000002</v>
+        <v>26.01</v>
       </c>
       <c r="G703" s="22">
         <v>392</v>
@@ -26617,7 +26617,7 @@
         <v>270</v>
       </c>
       <c r="F704" s="8">
-        <v>54.820700000000002</v>
+        <v>54.82</v>
       </c>
       <c r="G704" s="22">
         <v>493</v>
@@ -26640,7 +26640,7 @@
         <v>48</v>
       </c>
       <c r="F705" s="8">
-        <v>11.871500000000001</v>
+        <v>11.87</v>
       </c>
       <c r="G705" s="22">
         <v>404</v>
@@ -26663,7 +26663,7 @@
         <v>204</v>
       </c>
       <c r="F706" s="8">
-        <v>53.852500000000013</v>
+        <v>53.85</v>
       </c>
       <c r="G706" s="22">
         <v>379</v>
@@ -26686,7 +26686,7 @@
         <v>186</v>
       </c>
       <c r="F707" s="8">
-        <v>68.75200000000001</v>
+        <v>68.75</v>
       </c>
       <c r="G707" s="22">
         <v>271</v>
@@ -26709,7 +26709,7 @@
         <v>138</v>
       </c>
       <c r="F708" s="8">
-        <v>51.82820000000001</v>
+        <v>51.83</v>
       </c>
       <c r="G708" s="22">
         <v>266</v>
@@ -26732,7 +26732,7 @@
         <v>948</v>
       </c>
       <c r="F709" s="13">
-        <v>237.27749999999997</v>
+        <v>237.28</v>
       </c>
       <c r="G709" s="23">
         <v>400</v>
